--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.4%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.3%</t>
+          <t>-570.1%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-47.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-201.4%</t>
+          <t>-201.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-188.8%</t>
+          <t>-195.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-230.5%</t>
+          <t>-233.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-111.6%</t>
+          <t>-113.4%</t>
         </is>
       </c>
     </row>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.397652347571019</v>
+        <v>-5.334290414582497</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8055732161518598</v>
+        <v>0.8309179893472685</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5586644483112654</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.629791910507256</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288847462091292</v>
+        <v>-5.22548552910277</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8460932415637443</v>
+        <v>0.8714380147591529</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5586644483112654</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.626789981727249</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068826664054281</v>
+        <v>-5.00546473106576</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9356805977891627</v>
+        <v>0.9610253709845713</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4174446032432851</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.713100925778652</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935958974991004</v>
+        <v>-4.872597042002482</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.004721856216297</v>
+        <v>1.030066629411706</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4174446032432851</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.728995108580475</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.815785891626505</v>
+        <v>-4.752423958637984</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.053936934002398</v>
+        <v>1.079281707197807</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.2972715198787862</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.802244803039476</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.671113746526768</v>
+        <v>-4.607751813538246</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.121893894603733</v>
+        <v>1.147238667799142</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.1525993747790488</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.899136192660758</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73098857388446</v>
+        <v>-4.667626640895938</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.083981455062082</v>
+        <v>1.109326228257491</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2124742021367409</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.849248787647569</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.644189076105452</v>
+        <v>-4.580827143116929</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.141101747496251</v>
+        <v>1.166446520691661</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2124742021367409</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.871649280970135</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.646658782567258</v>
+        <v>-4.583296849578735</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.140186266284941</v>
+        <v>1.16553103948035</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.2149439085985471</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.870239858466463</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.715028968891268</v>
+        <v>-4.651667035902745</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.123845114230039</v>
+        <v>1.149189887425448</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.886812200362895</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.823567149807402</v>
+        <v>-4.760205216818879</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.070866550495477</v>
+        <v>1.096211323690886</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.877248908994786</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.854560309136107</v>
+        <v>-4.791198376147585</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8831788518043815</v>
+        <v>0.9085236249997906</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.701958474035173</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679086049343638</v>
+        <v>-4.615724116355116</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9579357877131569</v>
+        <v>0.9832805609085657</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.706525706026961</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790022301984887</v>
+        <v>-4.726660368996365</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8893033154178642</v>
+        <v>0.9146480886132733</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.682267734788168</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77321029711129</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.798304376129946</v>
+        <v>-4.734942443141423</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8891218709797464</v>
+        <v>0.9144666441751554</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.2139502837073905</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.661421552044959</v>
+        <v>2.680429875521038</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264159</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.738451756926223</v>
+        <v>-4.6750898239377</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9232353050933682</v>
+        <v>0.948580078288777</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.2139502837073905</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.671593938477091</v>
+        <v>2.69060226195317</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742295</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.652208293899845</v>
+        <v>-4.588846360911322</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9526789608777795</v>
+        <v>0.9780237340731885</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.2139502837073905</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.666540209050952</v>
+        <v>2.685548532527031</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.697515113298825</v>
+        <v>-4.634153180310302</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9263320085627131</v>
+        <v>0.9516767817581222</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.2547604467166213</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.633829886689939</v>
+        <v>2.652838210166018</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.726548218001126</v>
+        <v>-4.663186285012603</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9152706397148942</v>
+        <v>0.9406154129103033</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.2547604467166213</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.63438175972304</v>
+        <v>2.65339008319912</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.633737736550266</v>
+        <v>-4.570375803561744</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8816675241866037</v>
+        <v>0.9070122973820127</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1936305043925602</v>
+        <v>-0.1619499652657619</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.619340740484922</v>
+        <v>2.638349063961001</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.678127205879694</v>
+        <v>-4.614765272891171</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8657852123794336</v>
+        <v>0.8911299855748425</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2380199737219879</v>
+        <v>-0.2063394345951896</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.594580534811866</v>
+        <v>2.613588858287945</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.565455987643444</v>
+        <v>-4.502094054654921</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9059294081856566</v>
+        <v>0.9312741813810657</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0936682163589394</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.657258974265339</v>
+        <v>2.676267297741418</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.45307898646077</v>
+        <v>-4.389717053472248</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.956371504489393</v>
+        <v>0.9817162776848021</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0936682163589394</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.662750270096006</v>
+        <v>2.681758593572085</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.480859384362123</v>
+        <v>-4.417497451373601</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9567565470973911</v>
+        <v>0.9821013202928</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1531291533870907</v>
+        <v>-0.1214486142602925</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.657579233123733</v>
+        <v>2.676587556599813</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.563860665387402</v>
+        <v>-4.50049873239888</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7619117546879328</v>
+        <v>0.7872565278833417</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.1400194987874662</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.484792422408082</v>
+        <v>2.503800745884162</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.672474743830733</v>
+        <v>-4.609112810842211</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8386157840298059</v>
+        <v>0.8639605572252149</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.1400194987874662</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.604942083127288</v>
+        <v>2.623950406603367</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.759073326811836</v>
+        <v>-4.695711393823314</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8184893769396877</v>
+        <v>0.8438341501350968</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.1400194987874662</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.619455109229611</v>
+        <v>2.63846343270569</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.720689664253685</v>
+        <v>-4.657327731265163</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8312622833053169</v>
+        <v>0.8566070565007258</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.101635836229315</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.63990474810687</v>
+        <v>2.658913071582949</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.543573334218519</v>
+        <v>-4.480211401229997</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8988378441646852</v>
+        <v>0.9241826173600942</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.101635836229315</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.636633776952173</v>
+        <v>2.655642100428251</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.588665579052065</v>
+        <v>-4.525303646063542</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.88148433799318</v>
+        <v>0.9068291111885891</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1952124185255031</v>
+        <v>-0.1635318793987048</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.600179542812452</v>
+        <v>2.61918786628853</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.409290157813297</v>
+        <v>-4.345928224824775</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9470214817951015</v>
+        <v>0.9723662549905105</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03843566035478441</v>
+        <v>-0.006755121227986161</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.688032573021297</v>
+        <v>2.707040896497376</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.454304371333903</v>
+        <v>-4.39094243834538</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.909823251718449</v>
+        <v>0.9351680249138579</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06878455566938901</v>
+        <v>-0.03710401654259077</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.650630691164124</v>
+        <v>2.669639014640203</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.721308881606338</v>
+        <v>-4.657946948617815</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8087130099484208</v>
+        <v>0.8340577831438296</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2631475937123376</v>
+        <v>-0.2314670545855393</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.539704430677301</v>
+        <v>2.55871275415338</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.82250666304351</v>
+        <v>-4.759144730054988</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7674378192700531</v>
+        <v>0.7927825924654619</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.2998758681308585</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.497863064446611</v>
+        <v>2.51687138792269</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.790031076872738</v>
+        <v>-4.726669143884216</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7780280152926786</v>
+        <v>0.8033727884880877</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.2998758681308585</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.495463026000928</v>
+        <v>2.514471349477006</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.770992949165441</v>
+        <v>-4.707631016176919</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7821679855838424</v>
+        <v>0.8075127587792514</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.3580594794620531</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.457077578410455</v>
+        <v>2.476085901886535</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131247</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.802119580316059</v>
+        <v>-4.738757647327537</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9472992020622757</v>
+        <v>0.9726439752576845</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.3580594794620531</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.634659447349136</v>
+        <v>2.653667770825215</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.815986341649977</v>
+        <v>-4.752624408661455</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9425858265148421</v>
+        <v>0.967930599710251</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.395917396195876</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.612778026294976</v>
+        <v>2.631786349771055</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.836243640178935</v>
+        <v>-4.772881707190413</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9404914375001847</v>
+        <v>0.9658362106955938</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.395917396195876</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.618786556691902</v>
+        <v>2.637794880167981</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.688500669943933</v>
+        <v>-4.62513873695541</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.078741273386208</v>
+        <v>1.104086046581617</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.2281100389609929</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.798623618824854</v>
+        <v>2.817631942300933</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.790515352475154</v>
+        <v>-4.727153419486632</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.0407290219052</v>
+        <v>1.066073795100609</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.2281100389609929</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.801417240356335</v>
+        <v>2.820425563832414</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.78436264642237</v>
+        <v>-4.721000713433847</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.043852452717972</v>
+        <v>1.069197225913381</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2536378720350068</v>
+        <v>-0.2219573329082086</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.805771212379664</v>
+        <v>2.824779535855742</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.801171944572872</v>
+        <v>-4.737810011584349</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.036209210197882</v>
+        <v>1.061553983393291</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.2387666310587102</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.794766110229473</v>
+        <v>2.813774433705552</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.738873945796749</v>
+        <v>-4.675512012808227</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.127463963505152</v>
+        <v>1.152808736700561</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.2387666310587102</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861101664026294</v>
+        <v>2.880109987502373</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.537083748131591</v>
+        <v>-4.473721815143069</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9167609149606128</v>
+        <v>0.9421056881560217</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07242897801635406</v>
+        <v>-0.04074843888955582</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.688493451717184</v>
+        <v>2.707501775193264</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852419</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.477193066488998</v>
+        <v>-4.413831133500476</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.011007419939825</v>
+        <v>1.036352193135234</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01253829637376058</v>
+        <v>0.01914224275303766</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794718093024916</v>
+        <v>2.813726416500995</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.574933611113972</v>
+        <v>-4.51157167812545</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9865389382058791</v>
+        <v>1.011883711401288</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02842757450674077</v>
+        <v>0.003252964620057475</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799812262261171</v>
+        <v>2.81882058573725</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.751271371236902</v>
+        <v>-4.687909438248379</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9145398149813793</v>
+        <v>0.9398845881767881</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.1730847955028719</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.692545587012085</v>
+        <v>2.711553910488164</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.679725048460025</v>
+        <v>-4.616363115471502</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9416499621320584</v>
+        <v>0.9669947353274675</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.1730847955028719</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.691037205052014</v>
+        <v>2.710045528528093</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024958</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.635351916821456</v>
+        <v>-4.571989983832934</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9592620822229221</v>
+        <v>0.9846068554183312</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.1287116638643033</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717523951470591</v>
+        <v>2.73653227494667</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.82159115086322</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.627397946526684</v>
+        <v>-4.564036013538161</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.962443670340831</v>
+        <v>0.9877884435362401</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.1287116638643033</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.717523951470591</v>
+        <v>2.73653227494667</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947579</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.579742215965628</v>
+        <v>-4.516380282977106</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.987887719593058</v>
+        <v>1.013232492788467</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1127364724300459</v>
+        <v>-0.08105593330324767</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.752499146835029</v>
+        <v>2.771507470311108</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326872</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.452057906171332</v>
+        <v>-4.388695973182809</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.043853816885501</v>
+        <v>1.06919859008091</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.01494783736425054</v>
+        <v>0.04662837649104878</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.834002106086332</v>
+        <v>2.853010429562411</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314547</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.512724496573721</v>
+        <v>-4.449362563585199</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.006341853200418</v>
+        <v>1.031686626395827</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.06675047935428313</v>
+        <v>-0.03506994022748489</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.771737788531084</v>
+        <v>2.790746112007163</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690023</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.467886094965323</v>
+        <v>-4.4045241619768</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.028374916454406</v>
+        <v>1.053719689649815</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06220704640941366</v>
+        <v>-0.03052650728261541</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.778561550908634</v>
+        <v>2.797569874384713</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674307</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.568644730722321</v>
+        <v>-4.505282797733798</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9922324017826845</v>
+        <v>1.017577174978094</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1510326151364191</v>
+        <v>-0.1193520760096208</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.729427149303509</v>
+        <v>2.748435472779588</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163216</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.52444189363642</v>
+        <v>-4.461079960647898</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.015793139144882</v>
+        <v>1.041137912340291</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1068297780505186</v>
+        <v>-0.07514923892372039</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.761828454082886</v>
+        <v>2.780836777558966</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022901</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.561420921299863</v>
+        <v>-4.498058988311341</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9994115285487524</v>
+        <v>1.024756301744161</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0698558762591881</v>
+        <v>-0.03817533713238985</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.782422795626932</v>
+        <v>2.801431119103011</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042136</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.581479000164704</v>
+        <v>-4.518117067176181</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.042636062185856</v>
+        <v>1.067980835381265</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0698558762591881</v>
+        <v>-0.03817533713238985</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.833670560809972</v>
+        <v>2.852678884286051</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.541548326986813</v>
+        <v>-4.478186393998291</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.057049036051265</v>
+        <v>1.082393809246674</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02992520308129776</v>
+        <v>0.001755336045500488</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.856069669310959</v>
+        <v>2.875077992787038</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.490516234264286</v>
+        <v>-4.427154301275763</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.072410101378546</v>
+        <v>1.097754874573955</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.0211068896412302</v>
+        <v>0.05278742876802844</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.881637153182746</v>
+        <v>2.900645476658825</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.42529205313708</v>
+        <v>-4.361930120148558</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.115687177922133</v>
+        <v>1.141031951117542</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.08633107076843582</v>
+        <v>0.1180116098952341</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.937959065951774</v>
+        <v>2.956967389427853</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.387865033065946</v>
+        <v>-4.324503100077424</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.126618958249867</v>
+        <v>1.151963731445276</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.09158260879761748</v>
+        <v>0.1232631479244157</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.937070961068564</v>
+        <v>2.956079284544643</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.407976689100654</v>
+        <v>-4.344614756112132</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.119831088167224</v>
+        <v>1.145175861362633</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1026099537950367</v>
+        <v>0.1342904929218349</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.944944160398256</v>
+        <v>2.963952483874334</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.5056572683733</v>
+        <v>-4.442295335384777</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.241316627479377</v>
+        <v>1.266661400674786</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.008093241545152119</v>
+        <v>0.02358729758164613</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.039080014215353</v>
+        <v>3.058088337691432</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.481865699767157</v>
+        <v>-4.418503766778635</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.370946164139651</v>
+        <v>1.39629093733506</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.01569832706099017</v>
+        <v>0.04737886618778842</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.173467864596855</v>
+        <v>3.192476188072935</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756009</v>
+        <v>3.814259761756011</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.518620118328879</v>
+        <v>-4.455258185340357</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.347952372728821</v>
+        <v>1.37329714592423</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.01569832706099017</v>
+        <v>0.04737886618778842</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.165175840610714</v>
+        <v>3.184184164086794</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654184</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.514285815271831</v>
+        <v>-4.450923882283309</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.34787928953542</v>
+        <v>1.373224062730829</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1673484303801941</v>
+        <v>0.1990289695069923</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.254359098186016</v>
+        <v>3.273367421662095</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717114</v>
+        <v>3.796293177717116</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.505393353878548</v>
+        <v>-4.442031420890026</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.368990679819524</v>
+        <v>1.394335453014933</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1673484303801941</v>
+        <v>0.1990289695069923</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.271913503912808</v>
+        <v>3.290921827388887</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702624</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.673869470848426</v>
+        <v>-4.610507537859903</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.293455280436157</v>
+        <v>1.318800053631566</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1394005946636133</v>
+        <v>0.1710811337904116</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.246999849887443</v>
+        <v>3.266008173363522</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539966</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.976069941986843</v>
+        <v>-3.91270800899832</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.642987753437634</v>
+        <v>1.668332526633043</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.0690525352932026</v>
+        <v>0.1007330744200008</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.27520367572204</v>
+        <v>3.29421199919812</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389895</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.95334883830369</v>
+        <v>-3.889986905315168</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.6427402174078</v>
+        <v>1.668084990603209</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.0690525352932026</v>
+        <v>0.1007330744200008</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.265867698218945</v>
+        <v>3.284876021695024</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.83654770763417</v>
+        <v>3.846908012977684</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.087313665410055</v>
+        <v>-4.085314953329721</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.748060412416423</v>
+        <v>1.748859897248557</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.0649122918131626</v>
+        <v>-0.09459497359455288</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.344394927806295</v>
+        <v>3.326585318737461</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.6%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.1%</t>
+          <t>-570.8%</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.0%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-201.3%</t>
+          <t>-201.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-195.6%</t>
+          <t>-174.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-233.5%</t>
+          <t>-231.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-113.4%</t>
+          <t>-111.9%</t>
         </is>
       </c>
     </row>
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.334290414582497</v>
+        <v>-5.397652347571019</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8309179893472685</v>
+        <v>0.8055732161518598</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5586644483112654</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.629791910507256</v>
+        <v>2.610783587031177</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.22548552910277</v>
+        <v>-5.288847462091292</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8714380147591529</v>
+        <v>0.8460932415637443</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5586644483112654</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.626789981727249</v>
+        <v>2.607781658251171</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.00546473106576</v>
+        <v>-5.068826664054281</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9610253709845713</v>
+        <v>0.9356805977891627</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4174446032432851</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.713100925778652</v>
+        <v>2.694092602302573</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.872597042002482</v>
+        <v>-4.935958974991004</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.030066629411706</v>
+        <v>1.004721856216297</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4174446032432851</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.728995108580475</v>
+        <v>2.709986785104396</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.752423958637984</v>
+        <v>-4.815785891626505</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.079281707197807</v>
+        <v>1.053936934002398</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2972715198787862</v>
+        <v>-0.3289520590055844</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.802244803039476</v>
+        <v>2.783236479563397</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.607751813538246</v>
+        <v>-4.671113746526768</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.147238667799142</v>
+        <v>1.121893894603733</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1525993747790488</v>
+        <v>-0.184279913905847</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.899136192660758</v>
+        <v>2.88012786918468</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.667626640895938</v>
+        <v>-4.73098857388446</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.109326228257491</v>
+        <v>1.083981455062082</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2124742021367409</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.849248787647569</v>
+        <v>2.83024046417149</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.580827143116929</v>
+        <v>-4.644189076105452</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.166446520691661</v>
+        <v>1.141101747496251</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2124742021367409</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.871649280970135</v>
+        <v>2.852640957494056</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.583296849578735</v>
+        <v>-4.646658782567258</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.16553103948035</v>
+        <v>1.140186266284941</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2149439085985471</v>
+        <v>-0.2466244477253453</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.870239858466463</v>
+        <v>2.851231534990385</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.651667035902745</v>
+        <v>-4.715028968891268</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.149189887425448</v>
+        <v>1.123845114230039</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.886812200362895</v>
+        <v>2.867803876886815</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.760205216818879</v>
+        <v>-4.823567149807402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.096211323690886</v>
+        <v>1.070866550495477</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.877248908994786</v>
+        <v>2.858240585518707</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.791198376147585</v>
+        <v>-4.854560309136107</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9085236249997906</v>
+        <v>0.8831788518043815</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.701958474035173</v>
+        <v>2.682950150559094</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.615724116355116</v>
+        <v>-4.679086049343638</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9832805609085657</v>
+        <v>0.9579357877131569</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.706525706026961</v>
+        <v>2.687517382550881</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.726660368996365</v>
+        <v>-4.790022301984887</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9146480886132733</v>
+        <v>0.8893033154178642</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.682267734788168</v>
+        <v>2.663259411312088</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.734942443141423</v>
+        <v>-4.798304376129946</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9144666441751554</v>
+        <v>0.8891218709797464</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2139502837073905</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.680429875521038</v>
+        <v>2.661421552044959</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.6750898239377</v>
+        <v>-4.738451756926223</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.948580078288777</v>
+        <v>0.9232353050933682</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2139502837073905</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.69060226195317</v>
+        <v>2.671593938477091</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.588846360911322</v>
+        <v>-4.652208293899845</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9780237340731885</v>
+        <v>0.9526789608777795</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2139502837073905</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.685548532527031</v>
+        <v>2.666540209050952</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.634153180310302</v>
+        <v>-4.697515113298825</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9516767817581222</v>
+        <v>0.9263320085627131</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2547604467166213</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.652838210166018</v>
+        <v>2.633829886689939</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.663186285012603</v>
+        <v>-4.726548218001126</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9406154129103033</v>
+        <v>0.9152706397148942</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2547604467166213</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.65339008319912</v>
+        <v>2.63438175972304</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.570375803561744</v>
+        <v>-4.633737736550266</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9070122973820127</v>
+        <v>0.8816675241866037</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1619499652657619</v>
+        <v>-0.1936305043925602</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.638349063961001</v>
+        <v>2.619340740484922</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.614765272891171</v>
+        <v>-4.678127205879694</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8911299855748425</v>
+        <v>0.8657852123794336</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2063394345951896</v>
+        <v>-0.2380199737219879</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.613588858287945</v>
+        <v>2.594580534811866</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.502094054654921</v>
+        <v>-4.565455987643444</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9312741813810657</v>
+        <v>0.9059294081856566</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.0936682163589394</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.676267297741418</v>
+        <v>2.657258974265339</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.389717053472248</v>
+        <v>-4.45307898646077</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9817162776848021</v>
+        <v>0.956371504489393</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.0936682163589394</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.681758593572085</v>
+        <v>2.662750270096006</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.417497451373601</v>
+        <v>-4.480859384362123</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9821013202928</v>
+        <v>0.9567565470973911</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1214486142602925</v>
+        <v>-0.1531291533870907</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.676587556599813</v>
+        <v>2.657579233123733</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.50049873239888</v>
+        <v>-4.563860665387402</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7872565278833417</v>
+        <v>0.7619117546879328</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1400194987874662</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.503800745884162</v>
+        <v>2.484792422408082</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.609112810842211</v>
+        <v>-4.672474743830733</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8639605572252149</v>
+        <v>0.8386157840298059</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1400194987874662</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.623950406603367</v>
+        <v>2.604942083127288</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.695711393823314</v>
+        <v>-4.759073326811836</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8438341501350968</v>
+        <v>0.8184893769396877</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1400194987874662</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.63846343270569</v>
+        <v>2.619455109229611</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.657327731265163</v>
+        <v>-4.720689664253685</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8566070565007258</v>
+        <v>0.8312622833053169</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.101635836229315</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.658913071582949</v>
+        <v>2.63990474810687</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.480211401229997</v>
+        <v>-4.543573334218519</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9241826173600942</v>
+        <v>0.8988378441646852</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.101635836229315</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.655642100428251</v>
+        <v>2.636633776952173</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.525303646063542</v>
+        <v>-4.588665579052065</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9068291111885891</v>
+        <v>0.88148433799318</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1635318793987048</v>
+        <v>-0.1952124185255031</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.61918786628853</v>
+        <v>2.600179542812452</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.345928224824775</v>
+        <v>-4.409290157813297</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9723662549905105</v>
+        <v>0.9470214817951015</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.006755121227986161</v>
+        <v>-0.03843566035478441</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.707040896497376</v>
+        <v>2.688032573021297</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.39094243834538</v>
+        <v>-4.454304371333903</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9351680249138579</v>
+        <v>0.909823251718449</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.03710401654259077</v>
+        <v>-0.06878455566938901</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.669639014640203</v>
+        <v>2.650630691164124</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.657946948617815</v>
+        <v>-4.721308881606338</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8340577831438296</v>
+        <v>0.8087130099484208</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2314670545855393</v>
+        <v>-0.2631475937123376</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.55871275415338</v>
+        <v>2.539704430677301</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.759144730054988</v>
+        <v>-4.82250666304351</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7927825924654619</v>
+        <v>0.7674378192700531</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2998758681308585</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.51687138792269</v>
+        <v>2.497863064446611</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.726669143884216</v>
+        <v>-4.790031076872738</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8033727884880877</v>
+        <v>0.7780280152926786</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2998758681308585</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.514471349477006</v>
+        <v>2.495463026000928</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.707631016176919</v>
+        <v>-4.770992949165441</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8075127587792514</v>
+        <v>0.7821679855838424</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3580594794620531</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.476085901886535</v>
+        <v>2.457077578410455</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.738757647327537</v>
+        <v>-4.802119580316059</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9726439752576845</v>
+        <v>0.9472992020622757</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3580594794620531</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.653667770825215</v>
+        <v>2.634659447349136</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.752624408661455</v>
+        <v>-4.815986341649977</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.967930599710251</v>
+        <v>0.9425858265148421</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.395917396195876</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.631786349771055</v>
+        <v>2.612778026294976</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.772881707190413</v>
+        <v>-4.836243640178935</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9658362106955938</v>
+        <v>0.9404914375001847</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.395917396195876</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.637794880167981</v>
+        <v>2.618786556691902</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.62513873695541</v>
+        <v>-4.688500669943933</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.104086046581617</v>
+        <v>1.078741273386208</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2281100389609929</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.817631942300933</v>
+        <v>2.798623618824854</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.727153419486632</v>
+        <v>-4.790515352475154</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.066073795100609</v>
+        <v>1.0407290219052</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2281100389609929</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.820425563832414</v>
+        <v>2.801417240356335</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.721000713433847</v>
+        <v>-4.78436264642237</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.069197225913381</v>
+        <v>1.043852452717972</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2219573329082086</v>
+        <v>-0.2536378720350068</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.824779535855742</v>
+        <v>2.805771212379664</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.737810011584349</v>
+        <v>-4.801171944572872</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.061553983393291</v>
+        <v>1.036209210197882</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2387666310587102</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.813774433705552</v>
+        <v>2.794766110229473</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.675512012808227</v>
+        <v>-4.738873945796749</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.152808736700561</v>
+        <v>1.127463963505152</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2387666310587102</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.880109987502373</v>
+        <v>2.861101664026294</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.473721815143069</v>
+        <v>-4.537083748131591</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9421056881560217</v>
+        <v>0.9167609149606128</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.04074843888955582</v>
+        <v>-0.07242897801635406</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.707501775193264</v>
+        <v>2.688493451717184</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.413831133500476</v>
+        <v>-4.475528329303789</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.036352193135234</v>
+        <v>1.011673314813909</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.01914224275303766</v>
+        <v>-0.01087355918855215</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.813726416500995</v>
+        <v>2.795716935336041</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.51157167812545</v>
+        <v>-4.573268873928764</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.011883711401288</v>
+        <v>0.9872048330799628</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.003252964620057475</v>
+        <v>-0.02676283732153234</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.81882058573725</v>
+        <v>2.800811104572297</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.687909438248379</v>
+        <v>-4.749606634051693</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9398845881767881</v>
+        <v>0.9152057098554627</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1730847955028719</v>
+        <v>-0.2031005974444617</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.711553910488164</v>
+        <v>2.69354442932321</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.616363115471502</v>
+        <v>-4.678060311274816</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9669947353274675</v>
+        <v>0.9423158570061421</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1730847955028719</v>
+        <v>-0.2031005974444617</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.710045528528093</v>
+        <v>2.692036047363139</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024962</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.571989983832934</v>
+        <v>-4.633687179636247</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9846068554183312</v>
+        <v>0.9599279770970057</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1287116638643033</v>
+        <v>-0.1587274658058931</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.73653227494667</v>
+        <v>2.718522793781716</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.564036013538161</v>
+        <v>-4.625733209341475</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9877884435362401</v>
+        <v>0.9631095652149146</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1287116638643033</v>
+        <v>-0.1587274658058931</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.73653227494667</v>
+        <v>2.718522793781716</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.516380282977106</v>
+        <v>-4.578077478780419</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.013232492788467</v>
+        <v>0.9885536144671416</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.08105593330324767</v>
+        <v>-0.1110717352448375</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.771507470311108</v>
+        <v>2.753497989146154</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.388695973182809</v>
+        <v>-4.450393168986123</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.06919859008091</v>
+        <v>1.044519711759585</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.04662837649104878</v>
+        <v>0.01661257454945897</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.853010429562411</v>
+        <v>2.835000948397457</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.449362563585199</v>
+        <v>-4.511059759388512</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.031686626395827</v>
+        <v>1.007007748074501</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.03506994022748489</v>
+        <v>-0.0650857421690747</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.790746112007163</v>
+        <v>2.772736630842209</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.4045241619768</v>
+        <v>-4.466221357780114</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.053719689649815</v>
+        <v>1.029040811328489</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.03052650728261541</v>
+        <v>-0.06054230922420523</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.797569874384713</v>
+        <v>2.779560393219759</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.505282797733798</v>
+        <v>-4.566979993537112</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.017577174978094</v>
+        <v>0.9928982966567681</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1193520760096208</v>
+        <v>-0.1493678779512106</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.748435472779588</v>
+        <v>2.730425991614634</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.461079960647898</v>
+        <v>-4.522777156451212</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.041137912340291</v>
+        <v>1.016459034018965</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.07514923892372039</v>
+        <v>-0.1051650408653102</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.780836777558966</v>
+        <v>2.762827296394011</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.498058988311341</v>
+        <v>-4.559756184114654</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.024756301744161</v>
+        <v>1.000077423422836</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.03817533713238985</v>
+        <v>-0.06819113907397967</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.801431119103011</v>
+        <v>2.783421637938057</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.518117067176181</v>
+        <v>-4.579814262979495</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.067980835381265</v>
+        <v>1.043301957059939</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.03817533713238985</v>
+        <v>-0.06819113907397967</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.852678884286051</v>
+        <v>2.834669403121097</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.478186393998291</v>
+        <v>-4.539883589801605</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.082393809246674</v>
+        <v>1.057714930925349</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.001755336045500488</v>
+        <v>-0.02826046589608933</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.875077992787038</v>
+        <v>2.857068511622084</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.427154301275763</v>
+        <v>-4.488851497079077</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.097754874573955</v>
+        <v>1.07307599625263</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.05278742876802844</v>
+        <v>0.02277162682643863</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.900645476658825</v>
+        <v>2.882635995493871</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.361930120148558</v>
+        <v>-4.423627315951872</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.141031951117542</v>
+        <v>1.116353072796217</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1180116098952341</v>
+        <v>0.08799580795364426</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.956967389427853</v>
+        <v>2.938957908262899</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.324503100077424</v>
+        <v>-4.386200295880737</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.151963731445276</v>
+        <v>1.127284853123951</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1232631479244157</v>
+        <v>0.09324734598282591</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.956079284544643</v>
+        <v>2.938069803379689</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.344614756112132</v>
+        <v>-4.406311951915446</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.145175861362633</v>
+        <v>1.120496983041308</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1342904929218349</v>
+        <v>0.1042746909802451</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.963952483874334</v>
+        <v>2.94594300270938</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.442295335384777</v>
+        <v>-4.503992531188091</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.266661400674786</v>
+        <v>1.24198252235346</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.02358729758164613</v>
+        <v>-0.006428504359943688</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.058088337691432</v>
+        <v>3.040078856526478</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.418503766778635</v>
+        <v>-4.480200962581948</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.39629093733506</v>
+        <v>1.371612059013735</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04737886618778842</v>
+        <v>0.0173630642461986</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.192476188072935</v>
+        <v>3.174466706907981</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756011</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.455258185340357</v>
+        <v>-4.516955381143671</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.37329714592423</v>
+        <v>1.348618267602905</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04737886618778842</v>
+        <v>0.0173630642461986</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.184184164086794</v>
+        <v>3.16617468292184</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.450923882283309</v>
+        <v>-4.512621078086623</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.373224062730829</v>
+        <v>1.348545184409503</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1990289695069923</v>
+        <v>0.1690131675654025</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.273367421662095</v>
+        <v>3.255357940497142</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717116</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.442031420890026</v>
+        <v>-4.50372861669334</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.394335453014933</v>
+        <v>1.369656574693608</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1990289695069923</v>
+        <v>0.1690131675654025</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.290921827388887</v>
+        <v>3.272912346223933</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702624</v>
+        <v>3.794453975702626</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.610507537859903</v>
+        <v>-4.672204733663217</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.318800053631566</v>
+        <v>1.294121175310241</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1710811337904116</v>
+        <v>0.1410653318488218</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.266008173363522</v>
+        <v>3.247998692198568</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539967</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.91270800899832</v>
+        <v>-3.974405204801634</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.668332526633043</v>
+        <v>1.643653648311718</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1007330744200008</v>
+        <v>0.07071727247841103</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.29421199919812</v>
+        <v>3.276202518033166</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389897</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.889986905315168</v>
+        <v>-3.951684101118481</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.668084990603209</v>
+        <v>1.643406112281883</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1007330744200008</v>
+        <v>0.07071727247841103</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.284876021695024</v>
+        <v>3.26686654053007</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.846908012977684</v>
+        <v>3.759021142748677</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.085314953329721</v>
+        <v>-4.091976700655674</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.748859897248557</v>
+        <v>1.746195198318175</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.09459497359455288</v>
+        <v>-0.06957532705878161</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.326585318737461</v>
+        <v>3.341597106658924</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.6%</t>
+          <t>454.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.8%</t>
+          <t>-557.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-201.6%</t>
+          <t>-196.1%</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-174.3%</t>
+          <t>-189.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.0%</t>
+          <t>-231.1%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-111.9%</t>
+          <t>-112.0%</t>
         </is>
       </c>
     </row>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790022301984887</v>
+        <v>-4.650926660958918</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8893033154178642</v>
+        <v>0.9449415718282521</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2373487486891304</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.798304376129946</v>
+        <v>-4.659208735103976</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8891218709797464</v>
+        <v>0.9447601273901343</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2456308228341887</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.738451756926223</v>
+        <v>-4.599356115900253</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9232353050933682</v>
+        <v>0.9788735615037558</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2456308228341887</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.652208293899845</v>
+        <v>-4.513112652873875</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9526789608777795</v>
+        <v>1.008317217288167</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2456308228341887</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.697515113298825</v>
+        <v>-4.558419472272855</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9263320085627131</v>
+        <v>0.9819702649731008</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2864409858434195</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.726548218001126</v>
+        <v>-4.587452576975156</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9152706397148942</v>
+        <v>0.9709088961252821</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2864409858434195</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.633737736550266</v>
+        <v>-4.494642095524297</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8816675241866037</v>
+        <v>0.9373057805969915</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1936305043925602</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.678127205879694</v>
+        <v>-4.539031564853724</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8657852123794336</v>
+        <v>0.9214234687898213</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2380199737219879</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.565455987643444</v>
+        <v>-4.426360346617474</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9059294081856566</v>
+        <v>0.9615676645960445</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1253487554857377</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.45307898646077</v>
+        <v>-4.313983345434801</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.956371504489393</v>
+        <v>1.012009760899781</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1253487554857377</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.480859384362123</v>
+        <v>-4.341763743336154</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9567565470973911</v>
+        <v>1.012394803507779</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1531291533870907</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.563860665387402</v>
+        <v>-4.424765024361433</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7619117546879328</v>
+        <v>0.8175500110983205</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1717000379142645</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.672474743830733</v>
+        <v>-4.533379102804764</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8386157840298059</v>
+        <v>0.8942540404401937</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1717000379142645</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.759073326811836</v>
+        <v>-4.619977685785867</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8184893769396877</v>
+        <v>0.8741276333500756</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1717000379142645</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.720689664253685</v>
+        <v>-4.581594023227716</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8312622833053169</v>
+        <v>0.8869005397157046</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1333163753561133</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.543573334218519</v>
+        <v>-4.40447769319255</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8988378441646852</v>
+        <v>0.954476100575073</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1333163753561133</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.588665579052065</v>
+        <v>-4.449569938026095</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.88148433799318</v>
+        <v>0.9371225944035677</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1952124185255031</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.409290157813297</v>
+        <v>-4.270194516787328</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9470214817951015</v>
+        <v>1.002659738205489</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.03843566035478441</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.454304371333903</v>
+        <v>-4.315208730307933</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.909823251718449</v>
+        <v>0.9654615081288367</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.06878455566938901</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.721308881606338</v>
+        <v>-4.582213240580368</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8087130099484208</v>
+        <v>0.8643512663588084</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2631475937123376</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.82250666304351</v>
+        <v>-4.683411022017541</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7674378192700531</v>
+        <v>0.8230760756804407</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3315564072576568</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.790031076872738</v>
+        <v>-4.650935435846769</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7780280152926786</v>
+        <v>0.8336662717030663</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3315564072576568</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.770992949165441</v>
+        <v>-4.631897308139472</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7821679855838424</v>
+        <v>0.8378062419942303</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3897400185888513</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.802119580316059</v>
+        <v>-4.66302393929009</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9472992020622757</v>
+        <v>1.002937458472663</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3897400185888513</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.815986341649977</v>
+        <v>-4.676890700624008</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9425858265148421</v>
+        <v>0.9982240829252298</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4275979353226743</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.836243640178935</v>
+        <v>-4.697147999152966</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9404914375001847</v>
+        <v>0.9961296939105726</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4275979353226743</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.688500669943933</v>
+        <v>-4.549405028917963</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.078741273386208</v>
+        <v>1.134379529796596</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2597905780877911</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.790515352475154</v>
+        <v>-4.651419711449185</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.0407290219052</v>
+        <v>1.096367278315588</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2597905780877911</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.78436264642237</v>
+        <v>-4.6452670053964</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.043852452717972</v>
+        <v>1.09949070912836</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2536378720350068</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.801171944572872</v>
+        <v>-4.662076303546902</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.036209210197882</v>
+        <v>1.09184746660827</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2704471701855085</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.738873945796749</v>
+        <v>-4.59977830477078</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.127463963505152</v>
+        <v>1.183102219915539</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2704471701855085</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.537083748131591</v>
+        <v>-4.397988107105622</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9167609149606128</v>
+        <v>0.9723991713710005</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.07242897801635406</v>
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.475528329303789</v>
+        <v>-4.338097425463029</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.011673314813909</v>
+        <v>1.066645676350213</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01087355918855215</v>
+        <v>-0.01253829637376058</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.795716935336041</v>
+        <v>2.794718093024916</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.573268873928764</v>
+        <v>-4.435837970088003</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9872048330799628</v>
+        <v>1.042177194616267</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02676283732153234</v>
+        <v>-0.02842757450674077</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.800811104572297</v>
+        <v>2.799812262261171</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.749606634051693</v>
+        <v>-4.612175730210932</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9152057098554627</v>
+        <v>0.9701780713917669</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2031005974444617</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.69354442932321</v>
+        <v>2.692545587012085</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.678060311274816</v>
+        <v>-4.540629407434055</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9423158570061421</v>
+        <v>0.9972882185424463</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2031005974444617</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.692036047363139</v>
+        <v>2.691037205052014</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024962</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.633687179636247</v>
+        <v>-4.496256275795487</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9599279770970057</v>
+        <v>1.01490033863331</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1587274658058931</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.718522793781716</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.625733209341475</v>
+        <v>-4.488302305500715</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9631095652149146</v>
+        <v>1.018081926751219</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1587274658058931</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.718522793781716</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.578077478780419</v>
+        <v>-4.440646574939659</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9885536144671416</v>
+        <v>1.043525976003446</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1110717352448375</v>
+        <v>-0.1127364724300459</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.753497989146154</v>
+        <v>2.752499146835029</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.450393168986123</v>
+        <v>-4.312962265145362</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.044519711759585</v>
+        <v>1.099492073295889</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.01661257454945897</v>
+        <v>0.01494783736425054</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.835000948397457</v>
+        <v>2.834002106086332</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.511059759388512</v>
+        <v>-4.373628855547752</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.007007748074501</v>
+        <v>1.061980109610805</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.0650857421690747</v>
+        <v>-0.06675047935428313</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.772736630842209</v>
+        <v>2.771737788531084</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.466221357780114</v>
+        <v>-4.328790453939353</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.029040811328489</v>
+        <v>1.084013172864793</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06054230922420523</v>
+        <v>-0.06220704640941366</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.779560393219759</v>
+        <v>2.778561550908634</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.566979993537112</v>
+        <v>-4.429549089696351</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9928982966567681</v>
+        <v>1.047870658193072</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1493678779512106</v>
+        <v>-0.1510326151364191</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.730425991614634</v>
+        <v>2.729427149303509</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.522777156451212</v>
+        <v>-4.385346252610451</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.016459034018965</v>
+        <v>1.07143139555527</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1051650408653102</v>
+        <v>-0.1068297780505186</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.762827296394011</v>
+        <v>2.761828454082886</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.559756184114654</v>
+        <v>-4.422325280273894</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.000077423422836</v>
+        <v>1.05504978495914</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.06819113907397967</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.783421637938057</v>
+        <v>2.782422795626932</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.579814262979495</v>
+        <v>-4.442383359138734</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.043301957059939</v>
+        <v>1.098274318596244</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.06819113907397967</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.834669403121097</v>
+        <v>2.833670560809972</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.539883589801605</v>
+        <v>-4.402452685960844</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.057714930925349</v>
+        <v>1.112687292461653</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02826046589608933</v>
+        <v>-0.02992520308129776</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.857068511622084</v>
+        <v>2.856069669310959</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.488851497079077</v>
+        <v>-4.351420593238316</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.07307599625263</v>
+        <v>1.128048357788934</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.02277162682643863</v>
+        <v>0.0211068896412302</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.882635995493871</v>
+        <v>2.881637153182746</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.423627315951872</v>
+        <v>-4.286196412111111</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.116353072796217</v>
+        <v>1.171325434332521</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.08799580795364426</v>
+        <v>0.08633107076843582</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.938957908262899</v>
+        <v>2.937959065951774</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639817</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.386200295880737</v>
+        <v>-4.248769392039977</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.127284853123951</v>
+        <v>1.182257214660255</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.09324734598282591</v>
+        <v>0.09158260879761748</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.938069803379689</v>
+        <v>2.937070961068564</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.406311951915446</v>
+        <v>-4.268881048074685</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.120496983041308</v>
+        <v>1.175469344577612</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1042746909802451</v>
+        <v>0.1026099537950367</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.94594300270938</v>
+        <v>2.944944160398256</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.503992531188091</v>
+        <v>-4.36656162734733</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.24198252235346</v>
+        <v>1.296954883889764</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.006428504359943688</v>
+        <v>-0.008093241545152119</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.040078856526478</v>
+        <v>3.039080014215353</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.480200962581948</v>
+        <v>-4.342770058741188</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.371612059013735</v>
+        <v>1.426584420550039</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.0173630642461986</v>
+        <v>0.01569832706099017</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.174466706907981</v>
+        <v>3.173467864596855</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756011</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.516955381143671</v>
+        <v>-4.37952447730291</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.348618267602905</v>
+        <v>1.403590629139209</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.0173630642461986</v>
+        <v>0.01569832706099017</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.16617468292184</v>
+        <v>3.165175840610714</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.512621078086623</v>
+        <v>-4.375190174245862</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.348545184409503</v>
+        <v>1.403517545945808</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1690131675654025</v>
+        <v>0.1673484303801941</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.255357940497142</v>
+        <v>3.254359098186016</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.796293177717116</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.50372861669334</v>
+        <v>-4.366297712852579</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.369656574693608</v>
+        <v>1.424628936229912</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1690131675654025</v>
+        <v>0.1673484303801941</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.272912346223933</v>
+        <v>3.271913503912808</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702626</v>
+        <v>3.794453975702624</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.672204733663217</v>
+        <v>-4.534773829822456</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.294121175310241</v>
+        <v>1.349093536846545</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1410653318488218</v>
+        <v>0.1394005946636133</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.247998692198568</v>
+        <v>3.246999849887443</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.974405204801634</v>
+        <v>-3.836974300960873</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.643653648311718</v>
+        <v>1.698626009848022</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.07071727247841103</v>
+        <v>0.0690525352932026</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.276202518033166</v>
+        <v>3.27520367572204</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.951684101118481</v>
+        <v>-3.814253197277721</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.643406112281883</v>
+        <v>1.698378473818188</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.07071727247841103</v>
+        <v>0.0690525352932026</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.26686654053007</v>
+        <v>3.265867698218945</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.759021142748677</v>
+        <v>3.837461906107454</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.091976700655674</v>
+        <v>-3.954545796814913</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.746195198318175</v>
+        <v>1.80116755985448</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.06957532705878161</v>
+        <v>-0.07124006424399004</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.341597106658924</v>
+        <v>3.340598264347798</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-71.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.5%</t>
+          <t>453.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-557.0%</t>
+          <t>-565.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-196.1%</t>
+          <t>-199.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-189.5%</t>
+          <t>-179.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-231.1%</t>
+          <t>-228.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-112.0%</t>
+          <t>-113.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1999"/>
+  <dimension ref="A1:G2000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722815</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367683</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879965</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.397652347571019</v>
+        <v>-5.334290414582497</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8055732161518598</v>
+        <v>0.8309179893472685</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5586644483112654</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.629791910507256</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288847462091292</v>
+        <v>-5.22548552910277</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8460932415637443</v>
+        <v>0.8714380147591529</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5586644483112654</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.626789981727249</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068826664054281</v>
+        <v>-5.00546473106576</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9356805977891627</v>
+        <v>0.9610253709845713</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4174446032432851</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.713100925778652</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935958974991004</v>
+        <v>-4.872597042002482</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.004721856216297</v>
+        <v>1.030066629411706</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.4174446032432851</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.728995108580475</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.815785891626505</v>
+        <v>-4.752423958637984</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.053936934002398</v>
+        <v>1.079281707197807</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.2972715198787862</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.802244803039476</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.671113746526768</v>
+        <v>-4.607751813538246</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.121893894603733</v>
+        <v>1.147238667799142</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.1525993747790488</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.899136192660758</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73098857388446</v>
+        <v>-4.667626640895938</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.083981455062082</v>
+        <v>1.109326228257491</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2124742021367409</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.849248787647569</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.644189076105452</v>
+        <v>-4.580827143116929</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.141101747496251</v>
+        <v>1.166446520691661</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.2124742021367409</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.871649280970135</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.646658782567258</v>
+        <v>-4.583296849578735</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.140186266284941</v>
+        <v>1.16553103948035</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.2149439085985471</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.870239858466463</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.715028968891268</v>
+        <v>-4.651667035902745</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.123845114230039</v>
+        <v>1.149189887425448</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.886812200362895</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.823567149807402</v>
+        <v>-4.760205216818879</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.070866550495477</v>
+        <v>1.096211323690886</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.877248908994786</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.854560309136107</v>
+        <v>-4.791198376147585</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8831788518043815</v>
+        <v>0.9085236249997906</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.701958474035173</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679086049343638</v>
+        <v>-4.615724116355116</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9579357877131569</v>
+        <v>0.9832805609085657</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.706525706026961</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.650926660958918</v>
+        <v>-4.726660368996365</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9449415718282521</v>
+        <v>0.9146480886132733</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.2056682095623321</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.682267734788168</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.659208735103976</v>
+        <v>-4.734942443141423</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9447601273901343</v>
+        <v>0.9144666441751554</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.2139502837073905</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.661421552044959</v>
+        <v>2.680429875521038</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.599356115900253</v>
+        <v>-4.6750898239377</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9788735615037558</v>
+        <v>0.948580078288777</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.2139502837073905</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.671593938477091</v>
+        <v>2.69060226195317</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.513112652873875</v>
+        <v>-4.588846360911322</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.008317217288167</v>
+        <v>0.9780237340731885</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.2139502837073905</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.666540209050952</v>
+        <v>2.685548532527031</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.558419472272855</v>
+        <v>-4.634153180310302</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9819702649731008</v>
+        <v>0.9516767817581222</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.2547604467166213</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.633829886689939</v>
+        <v>2.652838210166018</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.587452576975156</v>
+        <v>-4.663186285012603</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9709088961252821</v>
+        <v>0.9406154129103033</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.2547604467166213</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.63438175972304</v>
+        <v>2.65339008319912</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.494642095524297</v>
+        <v>-4.570375803561744</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9373057805969915</v>
+        <v>0.9070122973820127</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1936305043925602</v>
+        <v>-0.1619499652657619</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.619340740484922</v>
+        <v>2.638349063961001</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.539031564853724</v>
+        <v>-4.614765272891171</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9214234687898213</v>
+        <v>0.8911299855748425</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2380199737219879</v>
+        <v>-0.2063394345951896</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.594580534811866</v>
+        <v>2.613588858287945</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.426360346617474</v>
+        <v>-4.502094054654921</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9615676645960445</v>
+        <v>0.9312741813810657</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0936682163589394</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.657258974265339</v>
+        <v>2.676267297741418</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.313983345434801</v>
+        <v>-4.389717053472248</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.012009760899781</v>
+        <v>0.9817162776848021</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0936682163589394</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.662750270096006</v>
+        <v>2.681758593572085</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.341763743336154</v>
+        <v>-4.417497451373601</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.012394803507779</v>
+        <v>0.9821013202928</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1531291533870907</v>
+        <v>-0.1214486142602925</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.657579233123733</v>
+        <v>2.676587556599813</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.424765024361433</v>
+        <v>-4.50049873239888</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8175500110983205</v>
+        <v>0.7872565278833417</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.1400194987874662</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.484792422408082</v>
+        <v>2.503800745884162</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.533379102804764</v>
+        <v>-4.609112810842211</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8942540404401937</v>
+        <v>0.8639605572252149</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.1400194987874662</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.604942083127288</v>
+        <v>2.623950406603367</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.619977685785867</v>
+        <v>-4.695711393823314</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8741276333500756</v>
+        <v>0.8438341501350968</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.1400194987874662</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.619455109229611</v>
+        <v>2.63846343270569</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.581594023227716</v>
+        <v>-4.657327731265163</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8869005397157046</v>
+        <v>0.8566070565007258</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.101635836229315</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.63990474810687</v>
+        <v>2.658913071582949</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.40447769319255</v>
+        <v>-4.480211401229997</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.954476100575073</v>
+        <v>0.9241826173600942</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.101635836229315</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.636633776952173</v>
+        <v>2.655642100428251</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.449569938026095</v>
+        <v>-4.525303646063542</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9371225944035677</v>
+        <v>0.9068291111885891</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1952124185255031</v>
+        <v>-0.1635318793987048</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.600179542812452</v>
+        <v>2.61918786628853</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.270194516787328</v>
+        <v>-4.345928224824775</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.002659738205489</v>
+        <v>0.9723662549905105</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03843566035478441</v>
+        <v>-0.006755121227986161</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.688032573021297</v>
+        <v>2.707040896497376</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.315208730307933</v>
+        <v>-4.39094243834538</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9654615081288367</v>
+        <v>0.9351680249138579</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06878455566938901</v>
+        <v>-0.03710401654259077</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.650630691164124</v>
+        <v>2.669639014640203</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.582213240580368</v>
+        <v>-4.657946948617815</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8643512663588084</v>
+        <v>0.8340577831438296</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2631475937123376</v>
+        <v>-0.2314670545855393</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.539704430677301</v>
+        <v>2.55871275415338</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.683411022017541</v>
+        <v>-4.759144730054988</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8230760756804407</v>
+        <v>0.7927825924654619</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.2998758681308585</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.497863064446611</v>
+        <v>2.51687138792269</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.650935435846769</v>
+        <v>-4.726669143884216</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8336662717030663</v>
+        <v>0.8033727884880877</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.2998758681308585</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.495463026000928</v>
+        <v>2.514471349477006</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.631897308139472</v>
+        <v>-4.707631016176919</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8378062419942303</v>
+        <v>0.8075127587792514</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.3580594794620531</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.457077578410455</v>
+        <v>2.476085901886535</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.66302393929009</v>
+        <v>-4.738757647327537</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.002937458472663</v>
+        <v>0.9726439752576845</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.3580594794620531</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.634659447349136</v>
+        <v>2.653667770825215</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.676890700624008</v>
+        <v>-4.752624408661455</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9982240829252298</v>
+        <v>0.967930599710251</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.395917396195876</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.612778026294976</v>
+        <v>2.631786349771055</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.697147999152966</v>
+        <v>-4.772881707190413</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9961296939105726</v>
+        <v>0.9658362106955938</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.395917396195876</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.618786556691902</v>
+        <v>2.637794880167981</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.549405028917963</v>
+        <v>-4.62513873695541</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.134379529796596</v>
+        <v>1.104086046581617</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.2281100389609929</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.798623618824854</v>
+        <v>2.817631942300933</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.651419711449185</v>
+        <v>-4.727153419486632</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.096367278315588</v>
+        <v>1.066073795100609</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.2281100389609929</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.801417240356335</v>
+        <v>2.820425563832414</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.6452670053964</v>
+        <v>-4.721000713433847</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.09949070912836</v>
+        <v>1.069197225913381</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2536378720350068</v>
+        <v>-0.2219573329082086</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.805771212379664</v>
+        <v>2.824779535855742</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.662076303546902</v>
+        <v>-4.737810011584349</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.09184746660827</v>
+        <v>1.061553983393291</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.2387666310587102</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.794766110229473</v>
+        <v>2.813774433705552</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.59977830477078</v>
+        <v>-4.675512012808227</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.183102219915539</v>
+        <v>1.152808736700561</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.2387666310587102</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861101664026294</v>
+        <v>2.880109987502373</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.397988107105622</v>
+        <v>-4.473721815143069</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9723991713710005</v>
+        <v>0.9421056881560217</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07242897801635406</v>
+        <v>-0.04074843888955582</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.688493451717184</v>
+        <v>2.707501775193264</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.338097425463029</v>
+        <v>-4.418538056656649</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.066645676350213</v>
+        <v>1.034469423872765</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01253829637376058</v>
+        <v>0.01443531959686428</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794718093024916</v>
+        <v>2.810902262607291</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.435837970088003</v>
+        <v>-4.516278601281623</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.042177194616267</v>
+        <v>1.010000942138819</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02842757450674077</v>
+        <v>-0.001453958536115907</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799812262261171</v>
+        <v>2.815996431843546</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.612175730210932</v>
+        <v>-4.692616361404553</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9701780713917669</v>
+        <v>0.9380018189143189</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.1777917186590453</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.692545587012085</v>
+        <v>2.70872975659446</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.540629407434055</v>
+        <v>-4.621070038627676</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9972882185424463</v>
+        <v>0.9651119660649981</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.1777917186590453</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.691037205052014</v>
+        <v>2.707221374634389</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83602339102496</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.496256275795487</v>
+        <v>-4.576696906989107</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.01490033863331</v>
+        <v>0.9827240861558617</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.1334185870204767</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717523951470591</v>
+        <v>2.733708121052966</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.488302305500715</v>
+        <v>-4.568742936694335</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.018081926751219</v>
+        <v>0.9859056742737706</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.1334185870204767</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.717523951470591</v>
+        <v>2.733708121052966</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.83304018194758</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.440646574939659</v>
+        <v>-4.521087206133279</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.043525976003446</v>
+        <v>1.011349723525998</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1127364724300459</v>
+        <v>-0.08576285645942106</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.752499146835029</v>
+        <v>2.768683316417404</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326873</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.312962265145362</v>
+        <v>-4.393402896338983</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.099492073295889</v>
+        <v>1.067315820818441</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.01494783736425054</v>
+        <v>0.0419214533348754</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.834002106086332</v>
+        <v>2.850186275668707</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314548</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.373628855547752</v>
+        <v>-4.454069486741371</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.061980109610805</v>
+        <v>1.029803857133358</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.06675047935428313</v>
+        <v>-0.03977686338365827</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.771737788531084</v>
+        <v>2.787921958113459</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.328790453939353</v>
+        <v>-4.409231085132973</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.084013172864793</v>
+        <v>1.051836920387346</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06220704640941366</v>
+        <v>-0.03523343043878879</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.778561550908634</v>
+        <v>2.794745720491009</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.429549089696351</v>
+        <v>-4.509989720889971</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.047870658193072</v>
+        <v>1.015694405715625</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1510326151364191</v>
+        <v>-0.1240589991657942</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.729427149303509</v>
+        <v>2.745611318885884</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.826713779163216</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.385346252610451</v>
+        <v>-4.46578688380407</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.07143139555527</v>
+        <v>1.039255143077822</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1068297780505186</v>
+        <v>-0.07985616207989377</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.761828454082886</v>
+        <v>2.778012623665261</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.422325280273894</v>
+        <v>-4.502765911467513</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.05504978495914</v>
+        <v>1.022873532481692</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0698558762591881</v>
+        <v>-0.04288226028856323</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.782422795626932</v>
+        <v>2.798606965209307</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.442383359138734</v>
+        <v>-4.522823990332354</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.098274318596244</v>
+        <v>1.066098066118796</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0698558762591881</v>
+        <v>-0.04288226028856323</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.833670560809972</v>
+        <v>2.849854730392347</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.402452685960844</v>
+        <v>-4.482893317154463</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.112687292461653</v>
+        <v>1.080511039984205</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02992520308129776</v>
+        <v>-0.002951587110672893</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.856069669310959</v>
+        <v>2.872253838893334</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.351420593238316</v>
+        <v>-4.431861224431936</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.128048357788934</v>
+        <v>1.095872105311486</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.0211068896412302</v>
+        <v>0.04808050561185506</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.881637153182746</v>
+        <v>2.897821322765121</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.286196412111111</v>
+        <v>-4.36663704330473</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.171325434332521</v>
+        <v>1.139149181855073</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.08633107076843582</v>
+        <v>0.1133046867390607</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.937959065951774</v>
+        <v>2.954143235534149</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639817</v>
+        <v>3.840090220639816</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.248769392039977</v>
+        <v>-4.329210023233596</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.182257214660255</v>
+        <v>1.150080962182807</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.09158260879761748</v>
+        <v>0.1185562247682423</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.937070961068564</v>
+        <v>2.953255130650938</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749918</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.268881048074685</v>
+        <v>-4.349321679268304</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.175469344577612</v>
+        <v>1.143293092100164</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1026099537950367</v>
+        <v>0.1295835697656615</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.944944160398256</v>
+        <v>2.96112832998063</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393544</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.36656162734733</v>
+        <v>-4.44700225854095</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.296954883889764</v>
+        <v>1.264778631412317</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.008093241545152119</v>
+        <v>0.01888037442547275</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.039080014215353</v>
+        <v>3.055264183797728</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714882</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.342770058741188</v>
+        <v>-4.423210689934807</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.426584420550039</v>
+        <v>1.394408168072591</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.01569832706099017</v>
+        <v>0.04267194303161503</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.173467864596855</v>
+        <v>3.189652034179231</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756011</v>
+        <v>3.814259761756008</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.37952447730291</v>
+        <v>-4.459965108496529</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.403590629139209</v>
+        <v>1.371414376661761</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.01569832706099017</v>
+        <v>0.04267194303161503</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.165175840610714</v>
+        <v>3.18136001019309</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654183</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.375190174245862</v>
+        <v>-4.455630805439482</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.403517545945808</v>
+        <v>1.37134129346836</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1673484303801941</v>
+        <v>0.194322046350819</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.254359098186016</v>
+        <v>3.270543267768391</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717116</v>
+        <v>3.796293177717113</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.366297712852579</v>
+        <v>-4.446738344046198</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.424628936229912</v>
+        <v>1.392452683752464</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1673484303801941</v>
+        <v>0.194322046350819</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.271913503912808</v>
+        <v>3.288097673495183</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702624</v>
+        <v>3.794453975702622</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.534773829822456</v>
+        <v>-4.615214461016076</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.349093536846545</v>
+        <v>1.316917284369097</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1394005946636133</v>
+        <v>0.1663742106342382</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.246999849887443</v>
+        <v>3.263184019469818</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539967</v>
+        <v>3.795603100539964</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.836974300960873</v>
+        <v>-3.917414932154493</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.698626009848022</v>
+        <v>1.666449757370574</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.0690525352932026</v>
+        <v>0.09602615126382746</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.27520367572204</v>
+        <v>3.291387845304415</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389897</v>
+        <v>3.784700379389894</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.814253197277721</v>
+        <v>-3.89469382847134</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.698378473818188</v>
+        <v>1.66620222134074</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.0690525352932026</v>
+        <v>0.09602615126382746</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.265867698218945</v>
+        <v>3.28205186780132</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,45 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.837461906107454</v>
+        <v>3.783234730534932</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.954545796814913</v>
+        <v>-4.034986428008533</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.80116755985448</v>
+        <v>1.768991307377032</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.07124006424399004</v>
+        <v>-0.04426644827336518</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.340598264347798</v>
+        <v>3.356782433930174</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="2" t="n">
+        <v>45462</v>
+      </c>
+      <c r="B2000" t="n">
+        <v>3.758985602041263</v>
+      </c>
+      <c r="C2000" t="n">
+        <v>3.332522124775364</v>
+      </c>
+      <c r="D2000" t="n">
+        <v>-4.034986428008533</v>
+      </c>
+      <c r="E2000" t="n">
+        <v>1.768991307377032</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>-0.04426644827336518</v>
+      </c>
+      <c r="G2000" t="n">
+        <v>3.325585921761732</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>34.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.0%</t>
+          <t>-69.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.1%</t>
+          <t>-543.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-199.3%</t>
+          <t>-190.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-179.4%</t>
+          <t>-287.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-228.4%</t>
+          <t>-221.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-113.5%</t>
+          <t>-100.8%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.291940510371528</v>
+        <v>-8.154983946995083</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1999704736397656</v>
+        <v>-0.1451878482891877</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.523452275399014</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.147011216768001</v>
+        <v>2.203090789583185</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.478660218680831</v>
+        <v>-8.341703655304386</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.27868466149789</v>
+        <v>-0.2239020361473116</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.523452275399014</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.142984912233598</v>
+        <v>2.199064485048782</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.861661607423462</v>
+        <v>-8.724705044047017</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4319873183165264</v>
+        <v>-0.3772046929659485</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.523452275399014</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.142882810912014</v>
+        <v>2.198962383727198</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.043531398408497</v>
+        <v>-8.906574835032051</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5021637187391104</v>
+        <v>-0.447381093388532</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.705322066384049</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.036332452292423</v>
+        <v>2.092412025107607</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.403061720912499</v>
+        <v>-9.266105157536053</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6406255444426607</v>
+        <v>-0.5858429190920824</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.705322066384049</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.041682755590473</v>
+        <v>2.097762328405657</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.453410784366721</v>
+        <v>-9.316454220990275</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6528491498671722</v>
+        <v>-0.5980665245165939</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.849137084530244</v>
+        <v>-1.755671129838271</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.019389337475118</v>
+        <v>2.075468910290302</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.551030061788117</v>
+        <v>-9.414073498411671</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6888551102139617</v>
+        <v>-0.6340724848633834</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.946756361951641</v>
+        <v>-1.853290407259667</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.963859521644048</v>
+        <v>2.019939094459232</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.69855614979376</v>
+        <v>-9.561599586417314</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7449719890946467</v>
+        <v>-0.6901893637440684</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.094282449957284</v>
+        <v>-2.000816495265311</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.878237425162234</v>
+        <v>1.934316997977418</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.902814325123623</v>
+        <v>-9.765857761747178</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8211620621079496</v>
+        <v>-0.7663794367573713</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.221921394571273</v>
+        <v>-2.1284554398793</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.807167255512484</v>
+        <v>1.863246828327667</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.977147301383788</v>
+        <v>-9.840190738007342</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8464126981275792</v>
+        <v>-0.7916300727770014</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.366620918505946</v>
+        <v>-2.273154963813973</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.724830095636116</v>
+        <v>1.7809096684513</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.903677469716339</v>
+        <v>-9.766720906339893</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8016530639671786</v>
+        <v>-0.7468704386166003</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.293151086838497</v>
+        <v>-2.199685132146524</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.784283696130006</v>
+        <v>1.84036326894519</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07880188710288</v>
+        <v>-9.941845323726437</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8571476101742794</v>
+        <v>-0.8023649848237011</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.374809549533068</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.693764266445597</v>
+        <v>1.74984383926078</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31325398111737</v>
+        <v>-10.17629741774093</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9581476126816715</v>
+        <v>-0.9033649873310927</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.374809549533068</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.686545101544001</v>
+        <v>1.742624674359184</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.41762871214382</v>
+        <v>-10.28067214876737</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.006569695866226</v>
+        <v>-0.9517870705156475</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.572650235251487</v>
+        <v>-2.479184280559514</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.617248072154157</v>
+        <v>1.673327644969341</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.47041486774414</v>
+        <v>-10.3334583043677</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.0265683682678</v>
+        <v>-0.9717857429172216</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.668325721833884</v>
+        <v>-2.574859767141911</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.560958570043275</v>
+        <v>1.617038142858459</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.59645166111243</v>
+        <v>-10.45949509773599</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.074289356986001</v>
+        <v>-1.019506731635423</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.549608144332169</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.578803272358235</v>
+        <v>1.634882845173419</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.54443614714362</v>
+        <v>-10.40747958376718</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.049492815712076</v>
+        <v>-0.9947101903614968</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.549608144332169</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.582793608044636</v>
+        <v>1.63887318085982</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.68610798886774</v>
+        <v>-10.5491514254913</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.107636779300465</v>
+        <v>-1.052854153949887</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.549608144332169</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.581318381145894</v>
+        <v>1.637397953961078</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.63651714444291</v>
+        <v>-10.49956058106646</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.072747031365659</v>
+        <v>-1.017964406015081</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.593483254599307</v>
+        <v>-2.500017299907335</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.626126297965667</v>
+        <v>1.682205870780851</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.62370975143813</v>
+        <v>-10.48675318806169</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.080675207810433</v>
+        <v>-1.025892582459854</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.642339029608209</v>
+        <v>-2.548873074916236</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.583761699313643</v>
+        <v>1.639841272128827</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.39786459871872</v>
+        <v>-10.26090803534228</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9807580736864598</v>
+        <v>-0.9259754483358811</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.506946399329072</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.61849677770215</v>
+        <v>1.674576350517334</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.27328594238113</v>
+        <v>-10.13632937900468</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9297874665953638</v>
+        <v>-0.8750048412447851</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.506946399329072</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.619635922258209</v>
+        <v>1.675715495073393</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.32618123042542</v>
+        <v>-10.18922466704897</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9483118076509713</v>
+        <v>-0.8935291823003917</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.501991053240626</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.625242904073384</v>
+        <v>1.681322476888568</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25404805513754</v>
+        <v>-10.11709149176109</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9137248332971817</v>
+        <v>-0.8589422079466029</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.501991053240626</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.630976608312021</v>
+        <v>1.687056181127205</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18268166252789</v>
+        <v>-10.04572509915144</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8949155386471883</v>
+        <v>-0.8401329132966096</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.430624660630978</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.664059181483945</v>
+        <v>1.720138754299128</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08922262854266</v>
+        <v>-9.952266065166217</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8674154063660064</v>
+        <v>-0.8126327810154272</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.430624660630978</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.654175700171037</v>
+        <v>1.710255272986221</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.821980827674267</v>
+        <v>-9.685024264297819</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7623532465180207</v>
+        <v>-0.707570621167442</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.430624660630978</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.652341139671663</v>
+        <v>1.708420712486847</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.724073788997776</v>
+        <v>-9.587117225621329</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7234907460208855</v>
+        <v>-0.6687081206703063</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.456104865462394</v>
+        <v>-2.362638910770421</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.692832274614536</v>
+        <v>1.74891184742972</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.700120248021818</v>
+        <v>-9.563163684645371</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7132408234850085</v>
+        <v>-0.6584581981344297</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.432151324486437</v>
+        <v>-2.338685369794464</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.707872905345605</v>
+        <v>1.763952478160788</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.436060309699021</v>
+        <v>-9.299103746322574</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6208771643176418</v>
+        <v>-0.5660945389670631</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.074625431471668</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.85304855217753</v>
+        <v>1.909128124992714</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839727</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.728980686194184</v>
+        <v>-8.592024122817737</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3408323485760079</v>
+        <v>-0.2860497232254291</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.074625431471668</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.850261518517229</v>
+        <v>1.906341091332413</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.688796387827994</v>
+        <v>-8.551839824451546</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3244150053416903</v>
+        <v>-0.2696323799911116</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.12790708779745</v>
+        <v>-2.034441133105477</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.874715721424785</v>
+        <v>1.930795294239969</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626476</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.52539651688863</v>
+        <v>-8.388439953512183</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.259688235745188</v>
+        <v>-0.2049056103946092</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.964507216858087</v>
+        <v>-1.871041262166115</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.972122465209159</v>
+        <v>2.028202038024343</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.291915294659031</v>
+        <v>-8.154958731282584</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.158371318015496</v>
+        <v>-0.1035886926649168</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731025994628489</v>
+        <v>-1.637560039936516</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.120135627384771</v>
+        <v>2.176215200199954</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.142248903651517</v>
+        <v>-8.005292340275069</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1013969719254493</v>
+        <v>-0.04661434657487007</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.638122503385953</v>
+        <v>-1.54465654869398</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172985511817333</v>
+        <v>2.229065084632517</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.009973430020629</v>
+        <v>-7.873016866644183</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05311929572606733</v>
+        <v>0.001663329624511434</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.505847029755066</v>
+        <v>-1.412381075063093</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247718282742892</v>
+        <v>2.303797855558076</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.819373755347477</v>
+        <v>-7.68241719197103</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02593563483083017</v>
+        <v>0.08071826018140937</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.221781400389941</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.364893148234421</v>
+        <v>2.420972721049604</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.570373956663896</v>
+        <v>-7.433417393287449</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1384418955279214</v>
+        <v>0.1932245208785006</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.221781400389941</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.377799489458079</v>
+        <v>2.433879062273263</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.675963946437</v>
+        <v>-7.539007383060554</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03177002998053879</v>
+        <v>0.02301259537003997</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.420837344855018</v>
+        <v>-1.327371390163045</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.186469565994998</v>
+        <v>2.242549138810182</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.694698848555597</v>
+        <v>-7.557742285179151</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.009280351049108404</v>
+        <v>0.06406297639968761</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.426433354515149</v>
+        <v>-1.332967399823176</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.231656302076006</v>
+        <v>2.287735874891189</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.546758807147998</v>
+        <v>-7.409802243771551</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05142255507601945</v>
+        <v>0.003360070274559757</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.406112438606591</v>
+        <v>-1.312646483914619</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.123969928932973</v>
+        <v>2.180049501748156</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.493789284894009</v>
+        <v>-7.356832721517563</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03894873242790187</v>
+        <v>0.0158338929226769</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.25967696166063</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.147037656031888</v>
+        <v>2.203117228847072</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.450240878123319</v>
+        <v>-7.313284314746872</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02848998181471885</v>
+        <v>0.02629264353585992</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.25967696166063</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.140077043936795</v>
+        <v>2.196156616751979</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.208092484669461</v>
+        <v>-7.071135921293014</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0828317299479675</v>
+        <v>0.1376143552985463</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.25967696166063</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.154539398317938</v>
+        <v>2.210618971133122</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.099833347546939</v>
+        <v>-6.962876784170493</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1206675052561712</v>
+        <v>0.17545013060675</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.25967696166063</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.149071518777133</v>
+        <v>2.205151091592317</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.976542212729808</v>
+        <v>-6.839585649353362</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1674820531936003</v>
+        <v>0.2222646785441791</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.229851781535472</v>
+        <v>-1.136385826843499</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.220544293677988</v>
+        <v>2.276623866493172</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.955393013826365</v>
+        <v>-6.818436450449918</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1836427109923027</v>
+        <v>0.2384253363428819</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.115236627940056</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.240934791257379</v>
+        <v>2.297014364072563</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.711627571842921</v>
+        <v>-6.574671008466474</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2769295961327312</v>
+        <v>0.3317122214833099</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.115236627940056</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.23671549960443</v>
+        <v>2.292795072419613</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.609864751565626</v>
+        <v>-6.472908188189179</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.319759038163665</v>
+        <v>0.3745416635142442</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.102017559547627</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246771254559903</v>
+        <v>2.302850827375087</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.360014357616551</v>
+        <v>-6.223057794240105</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4124412707269971</v>
+        <v>0.4672238960775759</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.102017559547627</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239513329543605</v>
+        <v>2.295592902358789</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.184122265149119</v>
+        <v>-6.047165701772673</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4863972312346188</v>
+        <v>0.5411798565851975</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.102017559547627</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.243112453064254</v>
+        <v>2.299192025879438</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.012675802126656</v>
+        <v>-5.875719238750209</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5683033224981577</v>
+        <v>0.6230859478487369</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.024037051217137</v>
+        <v>-0.930571096525164</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.359307836932286</v>
+        <v>2.415387409747469</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.938386236388316</v>
+        <v>-5.80142967301187</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5970396264097904</v>
+        <v>0.6518222517603696</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9497474854787973</v>
+        <v>-0.8562815307868248</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.402902053991586</v>
+        <v>2.45898162680677</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.874750494154382</v>
+        <v>-5.737793930777936</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6271887243576817</v>
+        <v>0.6819713497082605</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.7926457885528903</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.445778300386264</v>
+        <v>2.501857873201448</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.763323734828462</v>
+        <v>-5.626367171452015</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6529536868718453</v>
+        <v>0.7077363122224241</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.7926457885528903</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.42697255917006</v>
+        <v>2.483052131985243</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.522893238023602</v>
+        <v>-5.385936674647155</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7508689622186666</v>
+        <v>0.8056515875692458</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.55221529174803</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.572973933877853</v>
+        <v>2.629053506693037</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.450650669852407</v>
+        <v>-5.31369410647596</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7836953033219647</v>
+        <v>0.8384779286725439</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.55221529174803</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.576903247712674</v>
+        <v>2.632982820527857</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.334290414582497</v>
+        <v>-5.260695784194573</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8309179893472685</v>
+        <v>0.860355841502439</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5586644483112654</v>
+        <v>-0.4968790327460911</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.629791910507256</v>
+        <v>2.66686315984636</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.22548552910277</v>
+        <v>-5.151890898714846</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8714380147591529</v>
+        <v>0.9008758669143231</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5586644483112654</v>
+        <v>-0.4968790327460911</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.626789981727249</v>
+        <v>2.663861231066354</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.00546473106576</v>
+        <v>-4.931870100677835</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9610253709845713</v>
+        <v>0.9904632231397414</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4174446032432851</v>
+        <v>-0.3556591876781109</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.713100925778652</v>
+        <v>2.750172175117756</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.872597042002482</v>
+        <v>-4.799002411614557</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.030066629411706</v>
+        <v>1.059504481566876</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4174446032432851</v>
+        <v>-0.3556591876781109</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.728995108580475</v>
+        <v>2.76606635791958</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.752423958637984</v>
+        <v>-4.678829328250059</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.079281707197807</v>
+        <v>1.108719559352977</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2972715198787862</v>
+        <v>-0.2354861043136119</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.802244803039476</v>
+        <v>2.839316052378581</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.607751813538246</v>
+        <v>-4.534157183150321</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.147238667799142</v>
+        <v>1.176676519954312</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1525993747790488</v>
+        <v>-0.09081395921387453</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.899136192660758</v>
+        <v>2.936207441999863</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.667626640895938</v>
+        <v>-4.594032010508013</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.109326228257491</v>
+        <v>1.138764080412661</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2124742021367409</v>
+        <v>-0.1506887865715666</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.849248787647569</v>
+        <v>2.886320036986674</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.580827143116929</v>
+        <v>-4.507232512729005</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.166446520691661</v>
+        <v>1.19588437284683</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2124742021367409</v>
+        <v>-0.1506887865715666</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.871649280970135</v>
+        <v>2.90872053030924</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.583296849578735</v>
+        <v>-4.509702219190811</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.16553103948035</v>
+        <v>1.19496889163552</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2149439085985471</v>
+        <v>-0.1531584930333728</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.870239858466463</v>
+        <v>2.907311107805568</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.651667035902745</v>
+        <v>-4.578072405514821</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.149189887425448</v>
+        <v>1.178627739580618</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.1438827939971579</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.886812200362895</v>
+        <v>2.923883449701999</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.760205216818879</v>
+        <v>-4.686610586430955</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.096211323690886</v>
+        <v>1.125649175846056</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.1438827939971579</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.877248908994786</v>
+        <v>2.91432015833389</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.791198376147585</v>
+        <v>-4.717603745759661</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9085236249997906</v>
+        <v>0.9379614771549605</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.1438827939971579</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.701958474035173</v>
+        <v>2.739029723374277</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.615724116355116</v>
+        <v>-4.542129485967192</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9832805609085657</v>
+        <v>1.012718413063736</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.1438827939971579</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.706525706026961</v>
+        <v>2.743596955366065</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.726660368996365</v>
+        <v>-4.513970097582471</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9146480886132733</v>
+        <v>0.9997241971788311</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2056682095623321</v>
+        <v>-0.1438827939971579</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.682267734788168</v>
+        <v>2.719338984127272</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.734942443141423</v>
+        <v>-4.52225217172753</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9144666441751554</v>
+        <v>0.9995427527407132</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2139502837073905</v>
+        <v>-0.1521648681422162</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.680429875521038</v>
+        <v>2.717501124860143</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.6750898239377</v>
+        <v>-4.462399552523807</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.948580078288777</v>
+        <v>1.033656186854335</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2139502837073905</v>
+        <v>-0.1521648681422162</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.69060226195317</v>
+        <v>2.727673511292275</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.588846360911322</v>
+        <v>-4.376156089497429</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9780237340731885</v>
+        <v>1.063099842638746</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2139502837073905</v>
+        <v>-0.1521648681422162</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.685548532527031</v>
+        <v>2.722619781866135</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.634153180310302</v>
+        <v>-4.421462908896409</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9516767817581222</v>
+        <v>1.03675289032368</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2547604467166213</v>
+        <v>-0.192975031151447</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.652838210166018</v>
+        <v>2.689909459505123</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.663186285012603</v>
+        <v>-4.45049601359871</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9406154129103033</v>
+        <v>1.025691521475861</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2547604467166213</v>
+        <v>-0.192975031151447</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.65339008319912</v>
+        <v>2.690461332538224</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.570375803561744</v>
+        <v>-4.35768553214785</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9070122973820127</v>
+        <v>0.9920884059475705</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1619499652657619</v>
+        <v>-0.1001645497005877</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.638349063961001</v>
+        <v>2.675420313300105</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.614765272891171</v>
+        <v>-4.402075001477278</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8911299855748425</v>
+        <v>0.9762060941404003</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2063394345951896</v>
+        <v>-0.1445540190300154</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.613588858287945</v>
+        <v>2.650660107627049</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.502094054654921</v>
+        <v>-4.289403783241028</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9312741813810657</v>
+        <v>1.016350289946623</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.0936682163589394</v>
+        <v>-0.03188280079376515</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.676267297741418</v>
+        <v>2.713338547080522</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.389717053472248</v>
+        <v>-4.177026782058355</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9817162776848021</v>
+        <v>1.06679238625036</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.0936682163589394</v>
+        <v>-0.03188280079376515</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.681758593572085</v>
+        <v>2.71882984291119</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.417497451373601</v>
+        <v>-4.204807179959707</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9821013202928</v>
+        <v>1.067177428858358</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1214486142602925</v>
+        <v>-0.05966319869511821</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.676587556599813</v>
+        <v>2.713658805938917</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.50049873239888</v>
+        <v>-4.287808460984986</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7872565278833417</v>
+        <v>0.8723326364488995</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1400194987874662</v>
+        <v>-0.07823408322229197</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.503800745884162</v>
+        <v>2.540871995223266</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.609112810842211</v>
+        <v>-4.396422539428317</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8639605572252149</v>
+        <v>0.9490366657907727</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1400194987874662</v>
+        <v>-0.07823408322229197</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.623950406603367</v>
+        <v>2.661021655942472</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.695711393823314</v>
+        <v>-4.48302112240942</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8438341501350968</v>
+        <v>0.9289102587006544</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1400194987874662</v>
+        <v>-0.07823408322229197</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.63846343270569</v>
+        <v>2.675534682044795</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.657327731265163</v>
+        <v>-4.444637459851269</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8566070565007258</v>
+        <v>0.9416831650662836</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.101635836229315</v>
+        <v>-0.0398504206641408</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.658913071582949</v>
+        <v>2.695984320922054</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.480211401229997</v>
+        <v>-4.267521129816103</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9241826173600942</v>
+        <v>1.009258725925652</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.101635836229315</v>
+        <v>-0.0398504206641408</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.655642100428251</v>
+        <v>2.692713349767356</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.525303646063542</v>
+        <v>-4.312613374649649</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9068291111885891</v>
+        <v>0.9919052197541467</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1635318793987048</v>
+        <v>-0.1017464638335306</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.61918786628853</v>
+        <v>2.656259115627635</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.345928224824775</v>
+        <v>-4.133237953410881</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9723662549905105</v>
+        <v>1.057442363556068</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.006755121227986161</v>
+        <v>0.05503029433718809</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.707040896497376</v>
+        <v>2.744112145836481</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.39094243834538</v>
+        <v>-4.178252166931487</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9351680249138579</v>
+        <v>1.020244133479416</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.03710401654259077</v>
+        <v>0.02468139902258348</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.669639014640203</v>
+        <v>2.706710263979307</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.657946948617815</v>
+        <v>-4.445256677203922</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8340577831438296</v>
+        <v>0.9191338917093874</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2314670545855393</v>
+        <v>-0.1696816390203651</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.55871275415338</v>
+        <v>2.595784003492484</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.759144730054988</v>
+        <v>-4.546454458641095</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7927825924654619</v>
+        <v>0.8778587010310197</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2998758681308585</v>
+        <v>-0.2380904525656843</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.51687138792269</v>
+        <v>2.553942637261794</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.726669143884216</v>
+        <v>-4.513978872470322</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8033727884880877</v>
+        <v>0.8884488970536453</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2998758681308585</v>
+        <v>-0.2380904525656843</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.514471349477006</v>
+        <v>2.551542598816111</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.707631016176919</v>
+        <v>-4.494940744763025</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8075127587792514</v>
+        <v>0.8925888673448092</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3580594794620531</v>
+        <v>-0.2962740638968788</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.476085901886535</v>
+        <v>2.513157151225639</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.738757647327537</v>
+        <v>-4.526067375913644</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9726439752576845</v>
+        <v>1.057720083823242</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3580594794620531</v>
+        <v>-0.2962740638968788</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.653667770825215</v>
+        <v>2.69073902016432</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.752624408661455</v>
+        <v>-4.539934137247561</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.967930599710251</v>
+        <v>1.053006708275809</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.395917396195876</v>
+        <v>-0.3341319806307018</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.631786349771055</v>
+        <v>2.668857599110159</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.772881707190413</v>
+        <v>-4.560191435776519</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9658362106955938</v>
+        <v>1.050912319261152</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.395917396195876</v>
+        <v>-0.3341319806307018</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.637794880167981</v>
+        <v>2.674866129507085</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.62513873695541</v>
+        <v>-4.412448465541517</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.104086046581617</v>
+        <v>1.189162155147174</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2281100389609929</v>
+        <v>-0.1663246233958186</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.817631942300933</v>
+        <v>2.854703191640037</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.727153419486632</v>
+        <v>-4.514463148072738</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.066073795100609</v>
+        <v>1.151149903666167</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2281100389609929</v>
+        <v>-0.1663246233958186</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.820425563832414</v>
+        <v>2.857496813171518</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.721000713433847</v>
+        <v>-4.508310442019954</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.069197225913381</v>
+        <v>1.154273334478939</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2219573329082086</v>
+        <v>-0.1601719173430343</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.824779535855742</v>
+        <v>2.861850785194847</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.737810011584349</v>
+        <v>-4.525119740170456</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.061553983393291</v>
+        <v>1.146630091958849</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2387666310587102</v>
+        <v>-0.176981215493536</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.813774433705552</v>
+        <v>2.850845683044656</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.675512012808227</v>
+        <v>-4.462821741394333</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.152808736700561</v>
+        <v>1.237884845266118</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2387666310587102</v>
+        <v>-0.176981215493536</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.880109987502373</v>
+        <v>2.917181236841477</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.473721815143069</v>
+        <v>-4.261031543729175</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9421056881560217</v>
+        <v>1.027181796721579</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.04074843888955582</v>
+        <v>0.02103697667561844</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.707501775193264</v>
+        <v>2.744573024532368</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.418538056656649</v>
+        <v>-4.201140862086582</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.034469423872765</v>
+        <v>1.121428301700792</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.01443531959686428</v>
+        <v>0.08092765831821191</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.810902262607291</v>
+        <v>2.850797665840099</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.516278601281623</v>
+        <v>-4.298881406711557</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.010000942138819</v>
+        <v>1.096959819966846</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.001453958536115907</v>
+        <v>0.06503838018523173</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.815996431843546</v>
+        <v>2.855891835076355</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.692616361404553</v>
+        <v>-4.475219166834486</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9380018189143189</v>
+        <v>1.024960696742346</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1777917186590453</v>
+        <v>-0.1112993799376977</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.70872975659446</v>
+        <v>2.748625159827269</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.621070038627676</v>
+        <v>-4.403672844057609</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9651119660649981</v>
+        <v>1.052070843893025</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1777917186590453</v>
+        <v>-0.1112993799376977</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.707221374634389</v>
+        <v>2.747116777867197</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.576696906989107</v>
+        <v>-4.35929971241904</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9827240861558617</v>
+        <v>1.069682963983889</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1334185870204767</v>
+        <v>-0.06692624829912908</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.733708121052966</v>
+        <v>2.773603524285775</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863221</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.568742936694335</v>
+        <v>-4.351345742124268</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9859056742737706</v>
+        <v>1.072864552101798</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1334185870204767</v>
+        <v>-0.06692624829912908</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.733708121052966</v>
+        <v>2.773603524285775</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83304018194758</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.521087206133279</v>
+        <v>-4.303690011563212</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.011349723525998</v>
+        <v>1.098308601354025</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.08576285645942106</v>
+        <v>-0.01927051773807342</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.768683316417404</v>
+        <v>2.808578719650213</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326873</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.393402896338983</v>
+        <v>-4.176005701768916</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.067315820818441</v>
+        <v>1.154274698646468</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.0419214533348754</v>
+        <v>0.108413792056223</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.850186275668707</v>
+        <v>2.890081678901515</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314548</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.454069486741371</v>
+        <v>-4.236672292171305</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.029803857133358</v>
+        <v>1.116762734961384</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.03977686338365827</v>
+        <v>0.02671547533768936</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.787921958113459</v>
+        <v>2.827817361346268</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690024</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.409231085132973</v>
+        <v>-4.191833890562907</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.051836920387346</v>
+        <v>1.138795798215372</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.03523343043878879</v>
+        <v>0.03125890828255884</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.794745720491009</v>
+        <v>2.834641123723818</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674307</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.509989720889971</v>
+        <v>-4.292592526319905</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.015694405715625</v>
+        <v>1.102653283543651</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1240589991657942</v>
+        <v>-0.05756666044444658</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.745611318885884</v>
+        <v>2.785506722118693</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163216</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.46578688380407</v>
+        <v>-4.248389689234005</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.039255143077822</v>
+        <v>1.126214020905849</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.07985616207989377</v>
+        <v>-0.01336382335854613</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.778012623665261</v>
+        <v>2.81790802689807</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022901</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.502765911467513</v>
+        <v>-4.285368716897447</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.022873532481692</v>
+        <v>1.109832410309719</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.04288226028856323</v>
+        <v>0.0236100784327844</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.798606965209307</v>
+        <v>2.838502368442116</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042136</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.522823990332354</v>
+        <v>-4.305426795762288</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.066098066118796</v>
+        <v>1.153056943946822</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.04288226028856323</v>
+        <v>0.0236100784327844</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.849854730392347</v>
+        <v>2.889750133625155</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.482893317154463</v>
+        <v>-4.265496122584397</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.080511039984205</v>
+        <v>1.167469917812232</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.002951587110672893</v>
+        <v>0.06354075161067474</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.872253838893334</v>
+        <v>2.912149242126143</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.431861224431936</v>
+        <v>-4.21446402986187</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.095872105311486</v>
+        <v>1.182830983139513</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.04808050561185506</v>
+        <v>0.1145728443332027</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.897821322765121</v>
+        <v>2.937716725997929</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.36663704330473</v>
+        <v>-4.149239848734664</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.139149181855073</v>
+        <v>1.2261080596831</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1133046867390607</v>
+        <v>0.1797970254604083</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.954143235534149</v>
+        <v>2.994038638766958</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639816</v>
+        <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.329210023233596</v>
+        <v>-4.11181282866353</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.150080962182807</v>
+        <v>1.237039840010834</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1185562247682423</v>
+        <v>0.18504856348959</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.953255130650938</v>
+        <v>2.993150533883747</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.349321679268304</v>
+        <v>-4.131924484698239</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.143293092100164</v>
+        <v>1.230251969928191</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1295835697656615</v>
+        <v>0.1960759084870092</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.96112832998063</v>
+        <v>3.001023733213439</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393544</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.44700225854095</v>
+        <v>-4.229605063970884</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.264778631412317</v>
+        <v>1.351737509240343</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.01888037442547275</v>
+        <v>0.08537271314682038</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.055264183797728</v>
+        <v>3.095159587030536</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714882</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.423210689934807</v>
+        <v>-4.205813495364741</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.394408168072591</v>
+        <v>1.481367045900618</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04267194303161503</v>
+        <v>0.1091642817529627</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.189652034179231</v>
+        <v>3.229547437412039</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756008</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.459965108496529</v>
+        <v>-4.242567913926464</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.371414376661761</v>
+        <v>1.458373254489788</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04267194303161503</v>
+        <v>0.1091642817529627</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.18136001019309</v>
+        <v>3.221255413425898</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654183</v>
+        <v>3.803426852654186</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.455630805439482</v>
+        <v>-4.238233610869416</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.37134129346836</v>
+        <v>1.458300171296387</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.194322046350819</v>
+        <v>0.2608143850721666</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.270543267768391</v>
+        <v>3.3104386710012</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717113</v>
+        <v>3.796293177717117</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.446738344046198</v>
+        <v>-4.229341149476133</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.392452683752464</v>
+        <v>1.479411561580491</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.194322046350819</v>
+        <v>0.2608143850721666</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.288097673495183</v>
+        <v>3.327993076727991</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702622</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.615214461016076</v>
+        <v>-4.39781726644601</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.316917284369097</v>
+        <v>1.403876162197124</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1663742106342382</v>
+        <v>0.2328665493555858</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.263184019469818</v>
+        <v>3.303079422702627</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539964</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.917414932154493</v>
+        <v>-3.700017737584427</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.666449757370574</v>
+        <v>1.753408635198601</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.09602615126382746</v>
+        <v>0.1625184899851751</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.291387845304415</v>
+        <v>3.331283248537224</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389894</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.89469382847134</v>
+        <v>-3.677296633901274</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.66620222134074</v>
+        <v>1.753161099168767</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.09602615126382746</v>
+        <v>0.1625184899851751</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.28205186780132</v>
+        <v>3.321947271034129</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534932</v>
+        <v>3.783234730534935</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.034986428008533</v>
+        <v>-3.817589233438467</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.768991307377032</v>
+        <v>1.855950185205059</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.04426644827336518</v>
+        <v>0.02222589044798245</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.356782433930174</v>
+        <v>3.396677837162982</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.758985602041263</v>
+        <v>3.843726137788315</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.332522124775364</v>
+        <v>3.459309396833561</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.034986428008533</v>
+        <v>-3.817589233438467</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.768991307377032</v>
+        <v>1.855950185205059</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.04426644827336518</v>
+        <v>0.02222589044798245</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.325585921761732</v>
+        <v>3.452373193819929</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.0%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.4%</t>
+          <t>-70.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.6%</t>
+          <t>454.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-543.3%</t>
+          <t>-565.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-190.6%</t>
+          <t>-198.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-287.3%</t>
+          <t>-187.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-221.8%</t>
+          <t>-229.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-100.8%</t>
+          <t>-101.6%</t>
         </is>
       </c>
     </row>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.154983946995083</v>
+        <v>-8.291940510371528</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1451878482891877</v>
+        <v>-0.1999704736397656</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.523452275399014</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.203090789583185</v>
+        <v>2.147011216768001</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.341703655304386</v>
+        <v>-8.478660218680831</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2239020361473116</v>
+        <v>-0.27868466149789</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.523452275399014</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.199064485048782</v>
+        <v>2.142984912233598</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.724705044047017</v>
+        <v>-8.861661607423462</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3772046929659485</v>
+        <v>-0.4319873183165264</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.523452275399014</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.198962383727198</v>
+        <v>2.142882810912014</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.906574835032051</v>
+        <v>-9.043531398408497</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.447381093388532</v>
+        <v>-0.5021637187391104</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.705322066384049</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.092412025107607</v>
+        <v>2.036332452292423</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.266105157536053</v>
+        <v>-9.403061720912499</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5858429190920824</v>
+        <v>-0.6406255444426607</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.705322066384049</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.097762328405657</v>
+        <v>2.041682755590473</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.316454220990275</v>
+        <v>-9.453410784366721</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.5980665245165939</v>
+        <v>-0.6528491498671722</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.755671129838271</v>
+        <v>-1.849137084530244</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.075468910290302</v>
+        <v>2.019389337475118</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.414073498411671</v>
+        <v>-9.551030061788117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6340724848633834</v>
+        <v>-0.6888551102139617</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.853290407259667</v>
+        <v>-1.946756361951641</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.019939094459232</v>
+        <v>1.963859521644048</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.561599586417314</v>
+        <v>-9.69855614979376</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6901893637440684</v>
+        <v>-0.7449719890946467</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.000816495265311</v>
+        <v>-2.094282449957284</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.934316997977418</v>
+        <v>1.878237425162234</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.765857761747178</v>
+        <v>-9.902814325123623</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7663794367573713</v>
+        <v>-0.8211620621079496</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.1284554398793</v>
+        <v>-2.221921394571273</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.863246828327667</v>
+        <v>1.807167255512484</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.840190738007342</v>
+        <v>-9.977147301383788</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.7916300727770014</v>
+        <v>-0.8464126981275792</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.273154963813973</v>
+        <v>-2.366620918505946</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.7809096684513</v>
+        <v>1.724830095636116</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.766720906339893</v>
+        <v>-9.903677469716339</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7468704386166003</v>
+        <v>-0.8016530639671786</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.199685132146524</v>
+        <v>-2.293151086838497</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.84036326894519</v>
+        <v>1.784283696130006</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.941845323726437</v>
+        <v>-10.07880188710288</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8023649848237011</v>
+        <v>-0.8571476101742794</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.374809549533068</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.74984383926078</v>
+        <v>1.693764266445597</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.17629741774093</v>
+        <v>-10.31325398111737</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9033649873310927</v>
+        <v>-0.9581476126816715</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.374809549533068</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.742624674359184</v>
+        <v>1.686545101544001</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.28067214876737</v>
+        <v>-10.41762871214382</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.9517870705156475</v>
+        <v>-1.006569695866226</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.479184280559514</v>
+        <v>-2.572650235251487</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.673327644969341</v>
+        <v>1.617248072154157</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.3334583043677</v>
+        <v>-10.47041486774414</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.9717857429172216</v>
+        <v>-1.0265683682678</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.574859767141911</v>
+        <v>-2.668325721833884</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.617038142858459</v>
+        <v>1.560958570043275</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.45949509773599</v>
+        <v>-10.59645166111243</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.019506731635423</v>
+        <v>-1.074289356986001</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.549608144332169</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.634882845173419</v>
+        <v>1.578803272358235</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.40747958376718</v>
+        <v>-10.54443614714362</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.9947101903614968</v>
+        <v>-1.049492815712076</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.549608144332169</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.63887318085982</v>
+        <v>1.582793608044636</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.5491514254913</v>
+        <v>-10.68610798886774</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.052854153949887</v>
+        <v>-1.107636779300465</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.549608144332169</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.637397953961078</v>
+        <v>1.581318381145894</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.49956058106646</v>
+        <v>-10.63651714444291</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.017964406015081</v>
+        <v>-1.072747031365659</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.500017299907335</v>
+        <v>-2.593483254599307</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.682205870780851</v>
+        <v>1.626126297965667</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.48675318806169</v>
+        <v>-10.62370975143813</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.025892582459854</v>
+        <v>-1.080675207810433</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.548873074916236</v>
+        <v>-2.642339029608209</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.639841272128827</v>
+        <v>1.583761699313643</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.26090803534228</v>
+        <v>-10.39786459871872</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9259754483358811</v>
+        <v>-0.9807580736864598</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.506946399329072</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.674576350517334</v>
+        <v>1.61849677770215</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.13632937900468</v>
+        <v>-10.27328594238113</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.8750048412447851</v>
+        <v>-0.9297874665953638</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.506946399329072</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.675715495073393</v>
+        <v>1.619635922258209</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.18922466704897</v>
+        <v>-10.32618123042542</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.8935291823003917</v>
+        <v>-0.9483118076509713</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.501991053240626</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.681322476888568</v>
+        <v>1.625242904073384</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.11709149176109</v>
+        <v>-10.25404805513754</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8589422079466029</v>
+        <v>-0.9137248332971817</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.501991053240626</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.687056181127205</v>
+        <v>1.630976608312021</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.04572509915144</v>
+        <v>-10.18268166252789</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8401329132966096</v>
+        <v>-0.8949155386471883</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.430624660630978</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.720138754299128</v>
+        <v>1.664059181483945</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.952266065166217</v>
+        <v>-10.08922262854266</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8126327810154272</v>
+        <v>-0.8674154063660064</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.430624660630978</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.710255272986221</v>
+        <v>1.654175700171037</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.685024264297819</v>
+        <v>-9.821980827674267</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.707570621167442</v>
+        <v>-0.7623532465180207</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.430624660630978</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.708420712486847</v>
+        <v>1.652341139671663</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.587117225621329</v>
+        <v>-9.724073788997776</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6687081206703063</v>
+        <v>-0.7234907460208855</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.362638910770421</v>
+        <v>-2.456104865462394</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.74891184742972</v>
+        <v>1.692832274614536</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.563163684645371</v>
+        <v>-9.700120248021818</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6584581981344297</v>
+        <v>-0.7132408234850085</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.338685369794464</v>
+        <v>-2.432151324486437</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.763952478160788</v>
+        <v>1.707872905345605</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.299103746322574</v>
+        <v>-9.436060309699021</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5660945389670631</v>
+        <v>-0.6208771643176418</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.074625431471668</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.909128124992714</v>
+        <v>1.85304855217753</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.592024122817737</v>
+        <v>-8.728980686194184</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2860497232254291</v>
+        <v>-0.3408323485760079</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.074625431471668</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.906341091332413</v>
+        <v>1.850261518517229</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.551839824451546</v>
+        <v>-8.688796387827994</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2696323799911116</v>
+        <v>-0.3244150053416903</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.034441133105477</v>
+        <v>-2.12790708779745</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.930795294239969</v>
+        <v>1.874715721424785</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.388439953512183</v>
+        <v>-8.52539651688863</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2049056103946092</v>
+        <v>-0.259688235745188</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.871041262166115</v>
+        <v>-1.964507216858087</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.028202038024343</v>
+        <v>1.972122465209159</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.154958731282584</v>
+        <v>-8.291915294659031</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1035886926649168</v>
+        <v>-0.158371318015496</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.637560039936516</v>
+        <v>-1.731025994628489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.176215200199954</v>
+        <v>2.120135627384771</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.005292340275069</v>
+        <v>-8.142248903651517</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.04661434657487007</v>
+        <v>-0.1013969719254493</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.54465654869398</v>
+        <v>-1.638122503385953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.229065084632517</v>
+        <v>2.172985511817333</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.873016866644183</v>
+        <v>-8.009973430020629</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.001663329624511434</v>
+        <v>-0.05311929572606733</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.412381075063093</v>
+        <v>-1.505847029755066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.303797855558076</v>
+        <v>2.247718282742892</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.68241719197103</v>
+        <v>-7.819373755347477</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.08071826018140937</v>
+        <v>0.02593563483083017</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.221781400389941</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.420972721049604</v>
+        <v>2.364893148234421</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.433417393287449</v>
+        <v>-7.570373956663896</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1932245208785006</v>
+        <v>0.1384418955279214</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.221781400389941</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.433879062273263</v>
+        <v>2.377799489458079</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.539007383060554</v>
+        <v>-7.675963946437</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.02301259537003997</v>
+        <v>-0.03177002998053879</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.327371390163045</v>
+        <v>-1.420837344855018</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.242549138810182</v>
+        <v>2.186469565994998</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.557742285179151</v>
+        <v>-7.694698848555597</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.06406297639968761</v>
+        <v>0.009280351049108404</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.332967399823176</v>
+        <v>-1.426433354515149</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.287735874891189</v>
+        <v>2.231656302076006</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.409802243771551</v>
+        <v>-7.546758807147998</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.003360070274559757</v>
+        <v>-0.05142255507601945</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.312646483914619</v>
+        <v>-1.406112438606591</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.180049501748156</v>
+        <v>2.123969928932973</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.356832721517563</v>
+        <v>-7.493789284894009</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.0158338929226769</v>
+        <v>-0.03894873242790187</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.25967696166063</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.203117228847072</v>
+        <v>2.147037656031888</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.313284314746872</v>
+        <v>-7.450240878123319</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02629264353585992</v>
+        <v>-0.02848998181471885</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.25967696166063</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.196156616751979</v>
+        <v>2.140077043936795</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.071135921293014</v>
+        <v>-7.208092484669461</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1376143552985463</v>
+        <v>0.0828317299479675</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.25967696166063</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.210618971133122</v>
+        <v>2.154539398317938</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.962876784170493</v>
+        <v>-7.099833347546939</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.17545013060675</v>
+        <v>0.1206675052561712</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.25967696166063</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.205151091592317</v>
+        <v>2.149071518777133</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.839585649353362</v>
+        <v>-6.976542212729808</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2222646785441791</v>
+        <v>0.1674820531936003</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.136385826843499</v>
+        <v>-1.229851781535472</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.276623866493172</v>
+        <v>2.220544293677988</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.818436450449918</v>
+        <v>-6.955393013826365</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2384253363428819</v>
+        <v>0.1836427109923027</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.115236627940056</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.297014364072563</v>
+        <v>2.240934791257379</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.574671008466474</v>
+        <v>-6.711627571842921</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3317122214833099</v>
+        <v>0.2769295961327312</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.115236627940056</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.292795072419613</v>
+        <v>2.23671549960443</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.472908188189179</v>
+        <v>-6.609864751565626</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3745416635142442</v>
+        <v>0.319759038163665</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.102017559547627</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.302850827375087</v>
+        <v>2.246771254559903</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.223057794240105</v>
+        <v>-6.360014357616551</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4672238960775759</v>
+        <v>0.4124412707269971</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.102017559547627</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.295592902358789</v>
+        <v>2.239513329543605</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.047165701772673</v>
+        <v>-6.184122265149119</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5411798565851975</v>
+        <v>0.4863972312346188</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.102017559547627</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.299192025879438</v>
+        <v>2.243112453064254</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.875719238750209</v>
+        <v>-6.012675802126656</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6230859478487369</v>
+        <v>0.5683033224981577</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.930571096525164</v>
+        <v>-1.024037051217137</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.415387409747469</v>
+        <v>2.359307836932286</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.80142967301187</v>
+        <v>-5.938386236388316</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6518222517603696</v>
+        <v>0.5970396264097904</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8562815307868248</v>
+        <v>-0.9497474854787973</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.45898162680677</v>
+        <v>2.402902053991586</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.737793930777936</v>
+        <v>-5.874750494154382</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6819713497082605</v>
+        <v>0.6271887243576817</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7926457885528903</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.501857873201448</v>
+        <v>2.445778300386264</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.626367171452015</v>
+        <v>-5.763323734828462</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7077363122224241</v>
+        <v>0.6529536868718453</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7926457885528903</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.483052131985243</v>
+        <v>2.42697255917006</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.385936674647155</v>
+        <v>-5.522893238023602</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8056515875692458</v>
+        <v>0.7508689622186666</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.55221529174803</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.629053506693037</v>
+        <v>2.572973933877853</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.31369410647596</v>
+        <v>-5.450650669852407</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8384779286725439</v>
+        <v>0.7836953033219647</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.55221529174803</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.632982820527857</v>
+        <v>2.576903247712674</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.260695784194573</v>
+        <v>-5.397652347571019</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.860355841502439</v>
+        <v>0.8055732161518598</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4968790327460911</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.66686315984636</v>
+        <v>2.610783587031177</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.151890898714846</v>
+        <v>-5.288847462091292</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9008758669143231</v>
+        <v>0.8460932415637443</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4968790327460911</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.663861231066354</v>
+        <v>2.607781658251171</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.931870100677835</v>
+        <v>-5.068826664054281</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9904632231397414</v>
+        <v>0.9356805977891627</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3556591876781109</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.750172175117756</v>
+        <v>2.694092602302573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.799002411614557</v>
+        <v>-4.935958974991004</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.059504481566876</v>
+        <v>1.004721856216297</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3556591876781109</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.76606635791958</v>
+        <v>2.709986785104396</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.678829328250059</v>
+        <v>-4.815785891626505</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.108719559352977</v>
+        <v>1.053936934002398</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2354861043136119</v>
+        <v>-0.3289520590055844</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.839316052378581</v>
+        <v>2.783236479563397</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.534157183150321</v>
+        <v>-4.671113746526768</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.176676519954312</v>
+        <v>1.121893894603733</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.09081395921387453</v>
+        <v>-0.184279913905847</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.936207441999863</v>
+        <v>2.88012786918468</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.594032010508013</v>
+        <v>-4.73098857388446</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.138764080412661</v>
+        <v>1.083981455062082</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1506887865715666</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.886320036986674</v>
+        <v>2.83024046417149</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.507232512729005</v>
+        <v>-4.644189076105452</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.19588437284683</v>
+        <v>1.141101747496251</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1506887865715666</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.90872053030924</v>
+        <v>2.852640957494056</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.509702219190811</v>
+        <v>-4.646658782567258</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.19496889163552</v>
+        <v>1.140186266284941</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1531584930333728</v>
+        <v>-0.2466244477253453</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.907311107805568</v>
+        <v>2.851231534990385</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.578072405514821</v>
+        <v>-4.715028968891268</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.178627739580618</v>
+        <v>1.123845114230039</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1438827939971579</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.923883449701999</v>
+        <v>2.867803876886815</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.686610586430955</v>
+        <v>-4.823567149807402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.125649175846056</v>
+        <v>1.070866550495477</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1438827939971579</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.91432015833389</v>
+        <v>2.858240585518707</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.717603745759661</v>
+        <v>-4.854560309136107</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9379614771549605</v>
+        <v>0.8831788518043815</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1438827939971579</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.739029723374277</v>
+        <v>2.682950150559094</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.542129485967192</v>
+        <v>-4.679086049343638</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.012718413063736</v>
+        <v>0.9579357877131569</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1438827939971579</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.743596955366065</v>
+        <v>2.687517382550881</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.513970097582471</v>
+        <v>-4.790022301984887</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9997241971788311</v>
+        <v>0.8893033154178642</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1438827939971579</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.719338984127272</v>
+        <v>2.663259411312088</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.52225217172753</v>
+        <v>-4.798304376129946</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9995427527407132</v>
+        <v>0.8891218709797464</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1521648681422162</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.717501124860143</v>
+        <v>2.661421552044959</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.462399552523807</v>
+        <v>-4.738451756926223</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.033656186854335</v>
+        <v>0.9232353050933682</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1521648681422162</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.727673511292275</v>
+        <v>2.671593938477091</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.376156089497429</v>
+        <v>-4.652208293899845</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.063099842638746</v>
+        <v>0.9526789608777795</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1521648681422162</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.722619781866135</v>
+        <v>2.666540209050952</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.421462908896409</v>
+        <v>-4.697515113298825</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.03675289032368</v>
+        <v>0.9263320085627131</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.192975031151447</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.689909459505123</v>
+        <v>2.633829886689939</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.45049601359871</v>
+        <v>-4.726548218001126</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.025691521475861</v>
+        <v>0.9152706397148942</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.192975031151447</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.690461332538224</v>
+        <v>2.63438175972304</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.35768553214785</v>
+        <v>-4.633737736550266</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9920884059475705</v>
+        <v>0.8816675241866037</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1001645497005877</v>
+        <v>-0.1936305043925602</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.675420313300105</v>
+        <v>2.619340740484922</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.402075001477278</v>
+        <v>-4.678127205879694</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9762060941404003</v>
+        <v>0.8657852123794336</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1445540190300154</v>
+        <v>-0.2380199737219879</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.650660107627049</v>
+        <v>2.594580534811866</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.289403783241028</v>
+        <v>-4.565455987643444</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.016350289946623</v>
+        <v>0.9059294081856566</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.03188280079376515</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.713338547080522</v>
+        <v>2.657258974265339</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.177026782058355</v>
+        <v>-4.45307898646077</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.06679238625036</v>
+        <v>0.956371504489393</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.03188280079376515</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.71882984291119</v>
+        <v>2.662750270096006</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.204807179959707</v>
+        <v>-4.480859384362123</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.067177428858358</v>
+        <v>0.9567565470973911</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.05966319869511821</v>
+        <v>-0.1531291533870907</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.713658805938917</v>
+        <v>2.657579233123733</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.287808460984986</v>
+        <v>-4.563860665387402</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8723326364488995</v>
+        <v>0.7619117546879328</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.07823408322229197</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.540871995223266</v>
+        <v>2.484792422408082</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.396422539428317</v>
+        <v>-4.672474743830733</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9490366657907727</v>
+        <v>0.8386157840298059</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.07823408322229197</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.661021655942472</v>
+        <v>2.604942083127288</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.48302112240942</v>
+        <v>-4.759073326811836</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9289102587006544</v>
+        <v>0.8184893769396877</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.07823408322229197</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.675534682044795</v>
+        <v>2.619455109229611</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.444637459851269</v>
+        <v>-4.720689664253685</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9416831650662836</v>
+        <v>0.8312622833053169</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.0398504206641408</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.695984320922054</v>
+        <v>2.63990474810687</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.267521129816103</v>
+        <v>-4.543573334218519</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.009258725925652</v>
+        <v>0.8988378441646852</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.0398504206641408</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.692713349767356</v>
+        <v>2.636633776952173</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.312613374649649</v>
+        <v>-4.588665579052065</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9919052197541467</v>
+        <v>0.88148433799318</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1017464638335306</v>
+        <v>-0.1952124185255031</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.656259115627635</v>
+        <v>2.600179542812452</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011237</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.133237953410881</v>
+        <v>-4.409290157813297</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.057442363556068</v>
+        <v>0.9470214817951015</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.05503029433718809</v>
+        <v>-0.03843566035478441</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.744112145836481</v>
+        <v>2.688032573021297</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.178252166931487</v>
+        <v>-4.454304371333903</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.020244133479416</v>
+        <v>0.909823251718449</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.02468139902258348</v>
+        <v>-0.06878455566938901</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.706710263979307</v>
+        <v>2.650630691164124</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.445256677203922</v>
+        <v>-4.721308881606338</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9191338917093874</v>
+        <v>0.8087130099484208</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1696816390203651</v>
+        <v>-0.2631475937123376</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.595784003492484</v>
+        <v>2.539704430677301</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.546454458641095</v>
+        <v>-4.82250666304351</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8778587010310197</v>
+        <v>0.7674378192700531</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2380904525656843</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.553942637261794</v>
+        <v>2.497863064446611</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.513978872470322</v>
+        <v>-4.790031076872738</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8884488970536453</v>
+        <v>0.7780280152926786</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2380904525656843</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.551542598816111</v>
+        <v>2.495463026000928</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.494940744763025</v>
+        <v>-4.770992949165441</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8925888673448092</v>
+        <v>0.7821679855838424</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2962740638968788</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.513157151225639</v>
+        <v>2.457077578410455</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.526067375913644</v>
+        <v>-4.802119580316059</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.057720083823242</v>
+        <v>0.9472992020622757</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2962740638968788</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.69073902016432</v>
+        <v>2.634659447349136</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.539934137247561</v>
+        <v>-4.815986341649977</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.053006708275809</v>
+        <v>0.9425858265148421</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3341319806307018</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.668857599110159</v>
+        <v>2.612778026294976</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.560191435776519</v>
+        <v>-4.836243640178935</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.050912319261152</v>
+        <v>0.9404914375001847</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3341319806307018</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.674866129507085</v>
+        <v>2.618786556691902</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.412448465541517</v>
+        <v>-4.688500669943933</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.189162155147174</v>
+        <v>1.078741273386208</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1663246233958186</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.854703191640037</v>
+        <v>2.798623618824854</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.514463148072738</v>
+        <v>-4.790515352475154</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.151149903666167</v>
+        <v>1.0407290219052</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1663246233958186</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.857496813171518</v>
+        <v>2.801417240356335</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.969779300394455</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.508310442019954</v>
+        <v>-4.78436264642237</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.154273334478939</v>
+        <v>1.05567781751176</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1601719173430343</v>
+        <v>-0.2536378720350068</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.861850785194847</v>
+        <v>2.817596577173451</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.968859777134565</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.525119740170456</v>
+        <v>-4.801171944572872</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.146630091958849</v>
+        <v>1.048034574991669</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.176981215493536</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.850845683044656</v>
+        <v>2.80659147502326</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.035195330931386</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.462821741394333</v>
+        <v>-4.738873945796749</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.237884845266118</v>
+        <v>1.139289328298939</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.176981215493536</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.917181236841477</v>
+        <v>2.872927028820081</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.743776203320784</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.261031543729175</v>
+        <v>-4.537083748131591</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.027181796721579</v>
+        <v>0.9285862797544004</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.02103697667561844</v>
+        <v>-0.07242897801635406</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.744573024532368</v>
+        <v>2.700318816510972</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.814066435642959</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.201140862086582</v>
+        <v>-4.477193066488998</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.121428301700792</v>
+        <v>1.022832784733613</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.08092765831821191</v>
+        <v>-0.01253829637376058</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.850797665840099</v>
+        <v>2.806543457818703</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.828694171759003</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.298881406711557</v>
+        <v>-4.574933611113972</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.096959819966846</v>
+        <v>0.9983643029996667</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.06503838018523173</v>
+        <v>-0.02842757450674077</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.855891835076355</v>
+        <v>2.811637627054959</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.827230152583675</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.475219166834486</v>
+        <v>-4.751271371236902</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.024960696742346</v>
+        <v>0.9263651797751669</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1112993799376977</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.748625159827269</v>
+        <v>2.704370951805873</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.825721770623603</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.403672844057609</v>
+        <v>-4.679725048460025</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.052070843893025</v>
+        <v>0.953475326925846</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1112993799376977</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.747116777867197</v>
+        <v>2.702862569845801</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.825584638059039</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.35929971241904</v>
+        <v>-4.635351916821456</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.069682963983889</v>
+        <v>0.9710874470167097</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.06692624829912908</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.773603524285775</v>
+        <v>2.729349316264379</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.825584638059039</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.351345742124268</v>
+        <v>-4.627397946526684</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.072864552101798</v>
+        <v>0.9742690351346186</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.06692624829912908</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.773603524285775</v>
+        <v>2.729349316264379</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947582</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.831966395086844</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.303690011563212</v>
+        <v>-4.579742215965628</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.098308601354025</v>
+        <v>0.9997130843868451</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.01927051773807342</v>
+        <v>-0.1127364724300459</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.808578719650213</v>
+        <v>2.764324511628816</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.836858768461568</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.176005701768916</v>
+        <v>-4.452057906171332</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.154274698646468</v>
+        <v>1.055679181679289</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.108413792056223</v>
+        <v>0.01494783736425054</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.890081678901515</v>
+        <v>2.845827470880119</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.82883791131455</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.823613440937441</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.236672292171305</v>
+        <v>-4.512724496573721</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.116762734961384</v>
+        <v>1.018167217994205</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.02671547533768936</v>
+        <v>-0.06675047935428313</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.827817361346268</v>
+        <v>2.783563153324871</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.827711143548069</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.191833890562907</v>
+        <v>-4.467886094965323</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.138795798215372</v>
+        <v>1.040200281248193</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.03125890828255884</v>
+        <v>-0.06220704640941366</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.834641123723818</v>
+        <v>2.790386915702421</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.831872083179147</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.292592526319905</v>
+        <v>-4.568644730722321</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.102653283543651</v>
+        <v>1.004057766576472</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.05756666044444658</v>
+        <v>-0.1510326151364191</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.785506722118693</v>
+        <v>2.741252514097296</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.837751685706984</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.248389689234005</v>
+        <v>-4.52444189363642</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.126214020905849</v>
+        <v>1.027618503938669</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.01336382335854613</v>
+        <v>-0.1068297780505186</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.81790802689807</v>
+        <v>2.773653818876674</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.836161686176232</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.285368716897447</v>
+        <v>-4.561420921299863</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.109832410309719</v>
+        <v>1.01123689334254</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.0236100784327844</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.838502368442116</v>
+        <v>2.794248160420719</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.887409451359272</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.305426795762288</v>
+        <v>-4.581479000164704</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.153056943946822</v>
+        <v>1.054461426979643</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.0236100784327844</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.889750133625155</v>
+        <v>2.845495925603759</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.885850155953525</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.265496122584397</v>
+        <v>-4.541548326986813</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.167469917812232</v>
+        <v>1.068874400845052</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.06354075161067474</v>
+        <v>-0.02992520308129776</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.912149242126143</v>
+        <v>2.867895034104746</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.880798384191795</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.21446402986187</v>
+        <v>-4.490516234264286</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.182830983139513</v>
+        <v>1.084235466172333</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1145728443332027</v>
+        <v>0.0211068896412302</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.937716725997929</v>
+        <v>2.893462517976533</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.8979857882845</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.149239848734664</v>
+        <v>-4.42529205313708</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.2261080596831</v>
+        <v>1.12751254271592</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1797970254604083</v>
+        <v>0.08633107076843582</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.994038638766958</v>
+        <v>2.949784430745562</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639819</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.89394676058378</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.11181282866353</v>
+        <v>-4.387865033065946</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.237039840010834</v>
+        <v>1.138444323043654</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.18504856348959</v>
+        <v>0.09158260879761748</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.993150533883747</v>
+        <v>2.948896325862351</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.89520355291502</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.131924484698239</v>
+        <v>-4.355438858170709</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.230251969928191</v>
+        <v>1.152671585332989</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1960759084870092</v>
+        <v>0.1226157982466389</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.001023733213439</v>
+        <v>2.968773031863004</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.055761323936231</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.229605063970884</v>
+        <v>-4.453119437443355</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.351737509240343</v>
+        <v>1.274157124645142</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.08537271314682038</v>
+        <v>0.01191260290645013</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.095159587030536</v>
+        <v>3.062908885680101</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.175874233154048</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.205813495364741</v>
+        <v>-4.429327868837213</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.481367045900618</v>
+        <v>1.403786661305416</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1091642817529627</v>
+        <v>0.03570417151259242</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.229547437412039</v>
+        <v>3.197296736061604</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.814259761756011</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.167582209167907</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.242567913926464</v>
+        <v>-4.466082287398935</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.458373254489788</v>
+        <v>1.380792869894586</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1091642817529627</v>
+        <v>0.03570417151259242</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.221255413425898</v>
+        <v>3.189004712075463</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.165775404751687</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.238233610869416</v>
+        <v>-4.461747984341887</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.458300171296387</v>
+        <v>1.380719786701185</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2608143850721666</v>
+        <v>0.1873542748317963</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.3104386710012</v>
+        <v>3.278187969650765</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717116</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.183329810478478</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.229341149476133</v>
+        <v>-4.452855522948604</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.479411561580491</v>
+        <v>1.401831176985289</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2608143850721666</v>
+        <v>0.1873542748317963</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.327993076727991</v>
+        <v>3.295742375377556</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702624</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.175184857883062</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.39781726644601</v>
+        <v>-4.621331639918481</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.403876162197124</v>
+        <v>1.326295777601922</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2328665493555858</v>
+        <v>0.1594064391152156</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.303079422702627</v>
+        <v>3.270828721352192</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.245597519339906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.700017737584427</v>
+        <v>-3.923532111056898</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.753408635198601</v>
+        <v>1.675828250603399</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1625184899851751</v>
+        <v>0.08905837974480485</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.331283248537224</v>
+        <v>3.299032547186789</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.224436177043023</v>
+        <v>3.23626154183681</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.677296633901274</v>
+        <v>-3.900811007373746</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.753161099168767</v>
+        <v>1.675580714573565</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1625184899851751</v>
+        <v>0.08905837974480485</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.321947271034129</v>
+        <v>3.289696569683694</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534935</v>
+        <v>3.783234730534934</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.383342302894192</v>
+        <v>3.395167667687979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.817589233438467</v>
+        <v>-4.041103606910938</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.855950185205059</v>
+        <v>1.778369800609857</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.02222589044798245</v>
+        <v>-0.05123421979238779</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.396677837162982</v>
+        <v>3.364427135812547</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.843726137788315</v>
+        <v>3.822462606505824</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.459309396833561</v>
+        <v>3.450878395900192</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.817589233438467</v>
+        <v>-4.041103606910938</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.855950185205059</v>
+        <v>1.778369800609857</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.02222589044798245</v>
+        <v>-0.05123421979238779</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.452373193819929</v>
+        <v>3.443942192886559</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.7%</t>
+          <t>-565.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-198.4%</t>
+          <t>-199.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-101.6%</t>
+          <t>-102.8%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225446</v>
+        <v>3.765024323225448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793906</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011239</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.716991718982235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509542</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378103</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067869</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519913</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181175</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.969779300394455</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
         <v>-4.78436264642237</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05567781751176</v>
+        <v>1.043852452717972</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2536378720350068</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.817596577173451</v>
+        <v>2.805771212379664</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.968859777134565</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
         <v>-4.801171944572872</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.048034574991669</v>
+        <v>1.036209210197882</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2704471701855085</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.80659147502326</v>
+        <v>2.794766110229473</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.035195330931386</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
         <v>-4.738873945796749</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.139289328298939</v>
+        <v>1.127463963505152</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2704471701855085</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.872927028820081</v>
+        <v>2.861101664026294</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992196</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.743776203320784</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
         <v>-4.537083748131591</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9285862797544004</v>
+        <v>0.9167609149606128</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.07242897801635406</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.700318816510972</v>
+        <v>2.688493451717184</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.814066435642959</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
         <v>-4.477193066488998</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.022832784733613</v>
+        <v>1.011007419939825</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.01253829637376058</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.806543457818703</v>
+        <v>2.794718093024916</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319552</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.828694171759003</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
         <v>-4.574933611113972</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9983643029996667</v>
+        <v>0.9865389382058791</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.02842757450674077</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.811637627054959</v>
+        <v>2.799812262261171</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.827230152583675</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
         <v>-4.751271371236902</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9263651797751669</v>
+        <v>0.9145398149813793</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2047653346296702</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.704370951805873</v>
+        <v>2.692545587012085</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.825721770623603</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
         <v>-4.679725048460025</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.953475326925846</v>
+        <v>0.9416499621320584</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2047653346296702</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.702862569845801</v>
+        <v>2.691037205052014</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024966</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.825584638059039</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
         <v>-4.635351916821456</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9710874470167097</v>
+        <v>0.9592620822229221</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1603922029911016</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.729349316264379</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.825584638059039</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
         <v>-4.627397946526684</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9742690351346186</v>
+        <v>0.962443670340831</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1603922029911016</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.729349316264379</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947582</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.831966395086844</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
         <v>-4.579742215965628</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9997130843868451</v>
+        <v>0.987887719593058</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1127364724300459</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.764324511628816</v>
+        <v>2.752499146835029</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326878</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.836858768461568</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
         <v>-4.452057906171332</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.055679181679289</v>
+        <v>1.043853816885501</v>
       </c>
       <c r="F1979" t="n">
         <v>0.01494783736425054</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.845827470880119</v>
+        <v>2.834002106086332</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82883791131455</v>
+        <v>3.828837911314554</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.823613440937441</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
         <v>-4.512724496573721</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.018167217994205</v>
+        <v>1.006341853200418</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.06675047935428313</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.783563153324871</v>
+        <v>2.771737788531084</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.827711143548069</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
         <v>-4.467886094965323</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.040200281248193</v>
+        <v>1.028374916454406</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.06220704640941366</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.790386915702421</v>
+        <v>2.778561550908634</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.831872083179147</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
         <v>-4.568644730722321</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.004057766576472</v>
+        <v>0.9922324017826845</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.1510326151364191</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.741252514097296</v>
+        <v>2.729427149303509</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.837751685706984</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
         <v>-4.52444189363642</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.027618503938669</v>
+        <v>1.015793139144882</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1068297780505186</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.773653818876674</v>
+        <v>2.761828454082886</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.836161686176232</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
         <v>-4.561420921299863</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.01123689334254</v>
+        <v>0.9994115285487524</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.0698558762591881</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.794248160420719</v>
+        <v>2.782422795626932</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.887409451359272</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
         <v>-4.581479000164704</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.054461426979643</v>
+        <v>1.042636062185856</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.0698558762591881</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.845495925603759</v>
+        <v>2.833670560809972</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078284</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.885850155953525</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
         <v>-4.541548326986813</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.068874400845052</v>
+        <v>1.057049036051265</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.02992520308129776</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.867895034104746</v>
+        <v>2.856069669310959</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232401</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.880798384191795</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
         <v>-4.490516234264286</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.084235466172333</v>
+        <v>1.072410101378546</v>
       </c>
       <c r="F1987" t="n">
         <v>0.0211068896412302</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.893462517976533</v>
+        <v>2.881637153182746</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162116</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.8979857882845</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
         <v>-4.42529205313708</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.12751254271592</v>
+        <v>1.115687177922133</v>
       </c>
       <c r="F1988" t="n">
         <v>0.08633107076843582</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.949784430745562</v>
+        <v>2.937959065951774</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.84009022063982</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.89394676058378</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
         <v>-4.387865033065946</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.138444323043654</v>
+        <v>1.126618958249867</v>
       </c>
       <c r="F1989" t="n">
         <v>0.09158260879761748</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.948896325862351</v>
+        <v>2.937070961068564</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749924</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.89520355291502</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.355438858170709</v>
+        <v>-4.350021436758009</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.152671585332989</v>
+        <v>1.143013189104282</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1226157982466389</v>
+        <v>0.1226279049829371</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.968773031863004</v>
+        <v>2.956954931110996</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.82869047939355</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.055761323936231</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.453119437443355</v>
+        <v>-4.447702016030656</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.274157124645142</v>
+        <v>1.264498728416434</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.01191260290645013</v>
+        <v>0.01192470964274828</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.062908885680101</v>
+        <v>3.051090784928093</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714887</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.175874233154048</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.429327868837213</v>
+        <v>-4.423910447424513</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.403786661305416</v>
+        <v>1.394128265076709</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.03570417151259242</v>
+        <v>0.03571627824889057</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.197296736061604</v>
+        <v>3.185478635309596</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756011</v>
+        <v>3.814259761756014</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.167582209167907</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.466082287398935</v>
+        <v>-4.460664865986235</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.380792869894586</v>
+        <v>1.371134473665879</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.03570417151259242</v>
+        <v>0.03571627824889057</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.189004712075463</v>
+        <v>3.177186611323455</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654188</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.165775404751687</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.461747984341887</v>
+        <v>-4.456330562929187</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.380719786701185</v>
+        <v>1.371061390472478</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1873542748317963</v>
+        <v>0.1873663815680945</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.278187969650765</v>
+        <v>3.266369868898757</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717116</v>
+        <v>3.796293177717119</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.183329810478478</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.452855522948604</v>
+        <v>-4.447438101535904</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.401831176985289</v>
+        <v>1.392172780756582</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1873542748317963</v>
+        <v>0.1873663815680945</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.295742375377556</v>
+        <v>3.283924274625548</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702624</v>
+        <v>3.794453975702627</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.175184857883062</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.621331639918481</v>
+        <v>-4.615914218505782</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.326295777601922</v>
+        <v>1.316637381373215</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1594064391152156</v>
+        <v>0.1594185458515137</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.270828721352192</v>
+        <v>3.259010620600184</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539967</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.245597519339906</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.923532111056898</v>
+        <v>-3.918114689644198</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.675828250603399</v>
+        <v>1.666169854374692</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.08905837974480485</v>
+        <v>0.089070486481103</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.299032547186789</v>
+        <v>3.287214446434781</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389897</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.23626154183681</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.900811007373746</v>
+        <v>-3.895393585961046</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.675580714573565</v>
+        <v>1.665922318344858</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.08905837974480485</v>
+        <v>0.089070486481103</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.289696569683694</v>
+        <v>3.277878468931685</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534934</v>
+        <v>3.783234730534936</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.395167667687979</v>
+        <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.041103606910938</v>
+        <v>-4.035686185498238</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.778369800609857</v>
+        <v>1.76871140438115</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.05123421979238779</v>
+        <v>-0.05122211305608965</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.364427135812547</v>
+        <v>3.352609035060539</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.822462606505824</v>
+        <v>3.822462606505826</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.450878395900192</v>
+        <v>3.439053031106404</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.041103606910938</v>
+        <v>-4.035686185498238</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.778369800609857</v>
+        <v>1.76871140438115</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.05123421979238779</v>
+        <v>-0.05122211305608965</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.443942192886559</v>
+        <v>3.432116828092772</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>29.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,17 +864,17 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-69.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.4%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-565.1%</t>
+          <t>-543.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-199.4%</t>
+          <t>-191.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-187.5%</t>
+          <t>301.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-229.1%</t>
+          <t>-208.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-102.8%</t>
+          <t>-98.6%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839728</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.068826664054281</v>
+        <v>-5.151784769604504</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9356805977891627</v>
+        <v>0.9024973555690736</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.561899511676352</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.626427980718812</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.935958974991004</v>
+        <v>-5.018917080541226</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.004721856216297</v>
+        <v>0.9715386139962079</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.561899511676352</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.642322163520635</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.815785891626505</v>
+        <v>-4.898743997176727</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.053936934002398</v>
+        <v>1.020753691782309</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.441726428311853</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.715571857979636</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.671113746526768</v>
+        <v>-4.75407185207699</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.121893894603733</v>
+        <v>1.088710652383644</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.2970542832121156</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.812463247600919</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.73098857388446</v>
+        <v>-4.813946679434682</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.083981455062082</v>
+        <v>1.050798212841993</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.3569291105698078</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.762575842587729</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.644189076105452</v>
+        <v>-4.727147181655674</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.141101747496251</v>
+        <v>1.107918505276162</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.3569291105698078</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.784976335910295</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.646658782567258</v>
+        <v>-4.72961688811748</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.140186266284941</v>
+        <v>1.107003024064852</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.3593988170316139</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.783566913406624</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.715028968891268</v>
+        <v>-4.79798707444149</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.123845114230039</v>
+        <v>1.09066187200995</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.350123117995399</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.800139255303054</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.823567149807402</v>
+        <v>-4.906525255357624</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.070866550495477</v>
+        <v>1.037683308275388</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.350123117995399</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.790575963934946</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.854560309136107</v>
+        <v>-4.93751841468633</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8831788518043815</v>
+        <v>0.8499956095842927</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.350123117995399</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.615285528975333</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.679086049343638</v>
+        <v>-4.762044154893861</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9579357877131569</v>
+        <v>0.9247525454930678</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.350123117995399</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.61985276096712</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225448</v>
+        <v>3.765024323225447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.790022301984887</v>
+        <v>-4.87298040753511</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8893033154178642</v>
+        <v>0.8561200731977754</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.350123117995399</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.595594789728327</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.798304376129946</v>
+        <v>-4.881262481680168</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8891218709797464</v>
+        <v>0.8559386287596575</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.3584051921404574</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.661421552044959</v>
+        <v>2.593756930461198</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.738451756926223</v>
+        <v>-4.821409862476445</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9232353050933682</v>
+        <v>0.8900520628732791</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.3584051921404574</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.671593938477091</v>
+        <v>2.60392931689333</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.652208293899845</v>
+        <v>-4.735166399450067</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9526789608777795</v>
+        <v>0.9194957186576906</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.3584051921404574</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.666540209050952</v>
+        <v>2.59887558746719</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.697515113298825</v>
+        <v>-4.780473218849047</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9263320085627131</v>
+        <v>0.8931487663426241</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.3992153551496881</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.633829886689939</v>
+        <v>2.566165265106178</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.726548218001126</v>
+        <v>-4.809506323551348</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9152706397148942</v>
+        <v>0.8820873974948054</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.3992153551496881</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.63438175972304</v>
+        <v>2.566717138139279</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.633737736550266</v>
+        <v>-4.716695842100489</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8816675241866037</v>
+        <v>0.8484842819665148</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1936305043925602</v>
+        <v>-0.3064048736988288</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.619340740484922</v>
+        <v>2.551676118901161</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.678127205879694</v>
+        <v>-4.761085311429916</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8657852123794336</v>
+        <v>0.8326019701593446</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2380199737219879</v>
+        <v>-0.3507943430282565</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.594580534811866</v>
+        <v>2.526915913228104</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.565455987643444</v>
+        <v>-4.648414093193666</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9059294081856566</v>
+        <v>0.8727461659655678</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.2381231247920063</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.657258974265339</v>
+        <v>2.589594352681578</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.45307898646077</v>
+        <v>-4.536037092010993</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.956371504489393</v>
+        <v>0.9231882622693042</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.2381231247920063</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.662750270096006</v>
+        <v>2.595085648512245</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.480859384362123</v>
+        <v>-4.563817489912346</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9567565470973911</v>
+        <v>0.923573304877302</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1531291533870907</v>
+        <v>-0.2659035226933593</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.657579233123733</v>
+        <v>2.589914611539972</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.563860665387402</v>
+        <v>-4.646818770937625</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7619117546879328</v>
+        <v>0.7287285124678438</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.2844744072205331</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.484792422408082</v>
+        <v>2.417127800824321</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.672474743830733</v>
+        <v>-4.755432849380956</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8386157840298059</v>
+        <v>0.805432541809717</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.2844744072205331</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.604942083127288</v>
+        <v>2.537277461543527</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.759073326811836</v>
+        <v>-4.842031432362059</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8184893769396877</v>
+        <v>0.7853061347195989</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.2844744072205331</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.619455109229611</v>
+        <v>2.55179048764585</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.720689664253685</v>
+        <v>-4.803647769803908</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8312622833053169</v>
+        <v>0.7980790410852279</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.2460907446623819</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.63990474810687</v>
+        <v>2.572240126523109</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.543573334218519</v>
+        <v>-4.626531439768741</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8988378441646852</v>
+        <v>0.8656546019445963</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.2460907446623819</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.636633776952173</v>
+        <v>2.568969155368411</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793906</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.588665579052065</v>
+        <v>-4.671623684602287</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.88148433799318</v>
+        <v>0.848301095773091</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1952124185255031</v>
+        <v>-0.3079867878317717</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.600179542812452</v>
+        <v>2.532514921228691</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011239</v>
+        <v>3.750729377011237</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.409290157813297</v>
+        <v>-4.492248263363519</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9470214817951015</v>
+        <v>0.9138382395750124</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03843566035478441</v>
+        <v>-0.151210029661053</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.688032573021297</v>
+        <v>2.620367951437536</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982235</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.454304371333903</v>
+        <v>-4.537262476884125</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.909823251718449</v>
+        <v>0.87664000949836</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06878455566938901</v>
+        <v>-0.1815589249756576</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.650630691164124</v>
+        <v>2.582966069580363</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509542</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.721308881606338</v>
+        <v>-4.526360401043842</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8087130099484208</v>
+        <v>0.886692402173419</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2631475937123376</v>
+        <v>-0.1528454256908336</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.539704430677301</v>
+        <v>2.605885731490203</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.82250666304351</v>
+        <v>-4.627558182481015</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7674378192700531</v>
+        <v>0.8454172114950513</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.2212542392361528</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.497863064446611</v>
+        <v>2.564044365259513</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.790031076872738</v>
+        <v>-4.595082596310243</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7780280152926786</v>
+        <v>0.8560074075176769</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.2212542392361528</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.495463026000928</v>
+        <v>2.56164432681383</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378103</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.770992949165441</v>
+        <v>-4.576044468602945</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7821679855838424</v>
+        <v>0.8601473778088407</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.2794378505673473</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.457077578410455</v>
+        <v>2.523258879223358</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.802119580316059</v>
+        <v>-4.607171099753564</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9472992020622757</v>
+        <v>1.025278594287274</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.2794378505673473</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.634659447349136</v>
+        <v>2.700840748162038</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067869</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.815986341649977</v>
+        <v>-4.621037861087482</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9425858265148421</v>
+        <v>1.02056521873984</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.3172957673011703</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.612778026294976</v>
+        <v>2.678959327107878</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.836243640178935</v>
+        <v>-4.64129515961644</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9404914375001847</v>
+        <v>1.018470829725183</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.3172957673011703</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.618786556691902</v>
+        <v>2.684967857504804</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519913</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.688500669943933</v>
+        <v>-4.493552189381437</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.078741273386208</v>
+        <v>1.156720665611206</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.1494884100662871</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.798623618824854</v>
+        <v>2.864804919637756</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181175</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.790515352475154</v>
+        <v>-4.595566871912658</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.0407290219052</v>
+        <v>1.118708414130198</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.1494884100662871</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.801417240356335</v>
+        <v>2.867598541169237</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.78436264642237</v>
+        <v>-4.589414165859874</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.043852452717972</v>
+        <v>1.121831844942971</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2536378720350068</v>
+        <v>-0.1433357040135028</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.805771212379664</v>
+        <v>2.871952513192566</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.801171944572872</v>
+        <v>-4.606223464010376</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.036209210197882</v>
+        <v>1.11418860242288</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.1601450021640045</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.794766110229473</v>
+        <v>2.860947411042375</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.738873945796749</v>
+        <v>-4.543925465234254</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.127463963505152</v>
+        <v>1.20544335573015</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.1601450021640045</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861101664026294</v>
+        <v>2.927282964839196</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992196</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.537083748131591</v>
+        <v>-4.342135267569096</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9167609149606128</v>
+        <v>0.9947403071856111</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07242897801635406</v>
+        <v>0.03787319000514994</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.688493451717184</v>
+        <v>2.754674752530087</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.477193066488998</v>
+        <v>-4.282244585926502</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.011007419939825</v>
+        <v>1.088986812164824</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01253829637376058</v>
+        <v>0.09776387164774342</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794718093024916</v>
+        <v>2.860899393837818</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319552</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.574933611113972</v>
+        <v>-4.379985130551477</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9865389382058791</v>
+        <v>1.064518330430877</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02842757450674077</v>
+        <v>0.08187459351476323</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799812262261171</v>
+        <v>2.865993563074074</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.751271371236902</v>
+        <v>-4.556322890674406</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9145398149813793</v>
+        <v>0.9925192072063775</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.09446316660816617</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.692545587012085</v>
+        <v>2.758726887824988</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.679725048460025</v>
+        <v>-4.484776567897529</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9416499621320584</v>
+        <v>1.019629354357057</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.09446316660816617</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.691037205052014</v>
+        <v>2.757218505864916</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024966</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.635351916821456</v>
+        <v>-4.44040343625896</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9592620822229221</v>
+        <v>1.03724147444792</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.05009003496959757</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717523951470591</v>
+        <v>2.783705252283494</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.627397946526684</v>
+        <v>-4.432449465964188</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.962443670340831</v>
+        <v>1.040423062565829</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.05009003496959757</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.717523951470591</v>
+        <v>2.783705252283494</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947584</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.579742215965628</v>
+        <v>-4.384793735403132</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.987887719593058</v>
+        <v>1.065867111818056</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1127364724300459</v>
+        <v>-0.002434304408541921</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.752499146835029</v>
+        <v>2.818680447647932</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326878</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.452057906171332</v>
+        <v>-4.257109425608836</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.043853816885501</v>
+        <v>1.1218332091105</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.01494783736425054</v>
+        <v>0.1252500053857545</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.834002106086332</v>
+        <v>2.900183406899234</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314554</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.512724496573721</v>
+        <v>-4.317776016011225</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.006341853200418</v>
+        <v>1.084321245425417</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.06675047935428313</v>
+        <v>0.04355168866722087</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.771737788531084</v>
+        <v>2.837919089343986</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.467886094965323</v>
+        <v>-4.272937614402826</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.028374916454406</v>
+        <v>1.106354308679404</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06220704640941366</v>
+        <v>0.04809512161209034</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.778561550908634</v>
+        <v>2.844742851721537</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.568644730722321</v>
+        <v>-4.373696250159824</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9922324017826845</v>
+        <v>1.070211794007683</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1510326151364191</v>
+        <v>-0.04073044711491508</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.729427149303509</v>
+        <v>2.795608450116411</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.52444189363642</v>
+        <v>-4.329493413073924</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.015793139144882</v>
+        <v>1.093772531369881</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1068297780505186</v>
+        <v>0.003472389970985368</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.761828454082886</v>
+        <v>2.828009754895789</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.561420921299863</v>
+        <v>-4.366472440737367</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9994115285487524</v>
+        <v>1.077390920773751</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0698558762591881</v>
+        <v>0.0404462917623159</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.782422795626932</v>
+        <v>2.848604096439835</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.581479000164704</v>
+        <v>-4.386530519602207</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.042636062185856</v>
+        <v>1.120615454410854</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0698558762591881</v>
+        <v>0.0404462917623159</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.833670560809972</v>
+        <v>2.899851861622874</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078284</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.541548326986813</v>
+        <v>-4.346599846424317</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.057049036051265</v>
+        <v>1.135028428276264</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02992520308129776</v>
+        <v>0.08037696494020624</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.856069669310959</v>
+        <v>2.922250970123862</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232401</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.490516234264286</v>
+        <v>-4.295567753701789</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.072410101378546</v>
+        <v>1.150389493603545</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.0211068896412302</v>
+        <v>0.1314090576627342</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.881637153182746</v>
+        <v>2.947818453995648</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162116</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.42529205313708</v>
+        <v>-4.230343572574584</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.115687177922133</v>
+        <v>1.193666570147132</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.08633107076843582</v>
+        <v>0.1966332387899398</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.937959065951774</v>
+        <v>3.004140366764677</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84009022063982</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.387865033065946</v>
+        <v>-4.19291655250345</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.126618958249867</v>
+        <v>1.204598350474866</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.09158260879761748</v>
+        <v>0.2018847768191215</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.937070961068564</v>
+        <v>3.003252261881466</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749924</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.350021436758009</v>
+        <v>-4.213028208538158</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.143013189104282</v>
+        <v>1.197810480392223</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1226279049829371</v>
+        <v>0.2129121218165407</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.956954931110996</v>
+        <v>3.011125461211158</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82869047939355</v>
+        <v>3.828690479393548</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.447702016030656</v>
+        <v>-4.310708787810803</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.264498728416434</v>
+        <v>1.319296019704375</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.01192470964274828</v>
+        <v>0.1022089264763519</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.051090784928093</v>
+        <v>3.105261315028256</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714887</v>
+        <v>3.813251854714886</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.423910447424513</v>
+        <v>-4.286917219204661</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.394128265076709</v>
+        <v>1.44892555636465</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.03571627824889057</v>
+        <v>0.1260004950824942</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.185478635309596</v>
+        <v>3.239649165409758</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756014</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.460664865986235</v>
+        <v>-4.323671637766383</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.371134473665879</v>
+        <v>1.42593176495382</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.03571627824889057</v>
+        <v>0.1260004950824942</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.177186611323455</v>
+        <v>3.231357141423617</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654188</v>
+        <v>3.803426852654186</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.456330562929187</v>
+        <v>-4.319337334709335</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.371061390472478</v>
+        <v>1.425858681760418</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1873663815680945</v>
+        <v>0.2776505984016981</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.266369868898757</v>
+        <v>3.320540398998919</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717119</v>
+        <v>3.796293177717117</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.447438101535904</v>
+        <v>-4.310444873316052</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.392172780756582</v>
+        <v>1.446970072044523</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1873663815680945</v>
+        <v>0.2776505984016981</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.283924274625548</v>
+        <v>3.33809480472571</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702627</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.615914218505782</v>
+        <v>-4.478920990285929</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.316637381373215</v>
+        <v>1.371434672661156</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1594185458515137</v>
+        <v>0.2497027626851173</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.259010620600184</v>
+        <v>3.313181150700346</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.918114689644198</v>
+        <v>-3.781121461424346</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.666169854374692</v>
+        <v>1.720967145662633</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.089070486481103</v>
+        <v>0.1793547033147066</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.287214446434781</v>
+        <v>3.341384976534943</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.895393585961046</v>
+        <v>-3.758400357741194</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.665922318344858</v>
+        <v>1.720719609632799</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.089070486481103</v>
+        <v>0.1793547033147066</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.277878468931685</v>
+        <v>3.332048999031847</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783234730534936</v>
+        <v>3.885129387023484</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.035686185498238</v>
+        <v>-3.898692957278386</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.76871140438115</v>
+        <v>1.823508695669091</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.05122211305608965</v>
+        <v>0.03906210377751396</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.352609035060539</v>
+        <v>3.406779565160701</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.822462606505826</v>
+        <v>3.577673724346472</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.439053031106404</v>
+        <v>3.380912392875386</v>
       </c>
       <c r="D2000" t="n">
-        <v>-4.035686185498238</v>
+        <v>-3.81994907345022</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.76871140438115</v>
+        <v>1.852576339181551</v>
       </c>
       <c r="F2000" t="n">
-        <v>-0.05122211305608965</v>
+        <v>0.1550002467526382</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.432116828092772</v>
+        <v>3.473912540926969</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240619.xlsx
+++ b/tame_output/ON/bt/strategyON_20240619.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.6%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.1%</t>
+          <t>454.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-543.6%</t>
+          <t>-578.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-40.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-191.0%</t>
+          <t>-218.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>301.9%</t>
+          <t>-251.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-208.5%</t>
+          <t>-238.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-98.6%</t>
+          <t>-130.3%</t>
         </is>
       </c>
     </row>
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.043531398408497</v>
+        <v>-8.9867561177197</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5021637187391104</v>
+        <v>-0.4794536064635917</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.742012740387225</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.036332452292423</v>
+        <v>2.070397620705701</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.403061720912499</v>
+        <v>-9.346286440223702</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6406255444426607</v>
+        <v>-0.6179154321671421</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.742012740387225</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.041682755590473</v>
+        <v>2.075747924003752</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.453410784366721</v>
+        <v>-9.396635503677924</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6528491498671722</v>
+        <v>-0.6301390375916536</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.849137084530244</v>
+        <v>-1.792361803841447</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.019389337475118</v>
+        <v>2.053454505888396</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.551030061788117</v>
+        <v>-9.49425478109932</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6888551102139617</v>
+        <v>-0.6661449979384431</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.946756361951641</v>
+        <v>-1.889981081262843</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.963859521644048</v>
+        <v>1.997924690057327</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.69855614979376</v>
+        <v>-9.641780869104963</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7449719890946467</v>
+        <v>-0.722261876819128</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.094282449957284</v>
+        <v>-2.037507169268487</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.878237425162234</v>
+        <v>1.912302593575513</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.902814325123623</v>
+        <v>-9.846039044434827</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8211620621079496</v>
+        <v>-0.798451949832431</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.221921394571273</v>
+        <v>-2.165146113882476</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.807167255512484</v>
+        <v>1.841232423925762</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.977147301383788</v>
+        <v>-9.920372020694991</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8464126981275792</v>
+        <v>-0.8237025858520606</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.366620918505946</v>
+        <v>-2.309845637817149</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.724830095636116</v>
+        <v>1.758895264049394</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.903677469716339</v>
+        <v>-9.846902189027542</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8016530639671786</v>
+        <v>-0.7789429516916599</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.293151086838497</v>
+        <v>-2.2363758061497</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.784283696130006</v>
+        <v>1.818348864543284</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07880188710288</v>
+        <v>-10.02202660641409</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8571476101742794</v>
+        <v>-0.8344374978987608</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.411500223536244</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.693764266445597</v>
+        <v>1.727829434858875</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31325398111737</v>
+        <v>-10.25647870042858</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9581476126816715</v>
+        <v>-0.9354375004061528</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.411500223536244</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.686545101544001</v>
+        <v>1.720610269957279</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.41762871214382</v>
+        <v>-10.36085343145502</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.006569695866226</v>
+        <v>-0.9838595835907076</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.572650235251487</v>
+        <v>-2.51587495456269</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.617248072154157</v>
+        <v>1.651313240567435</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.47041486774414</v>
+        <v>-10.41363958705535</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.0265683682678</v>
+        <v>-1.003858255992282</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.668325721833884</v>
+        <v>-2.611550441145087</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.560958570043275</v>
+        <v>1.595023738456553</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.59645166111243</v>
+        <v>-10.53967638042364</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.074289356986001</v>
+        <v>-1.051579244710483</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.586298818335345</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.578803272358235</v>
+        <v>1.612868440771513</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.54443614714362</v>
+        <v>-10.48766086645482</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.049492815712076</v>
+        <v>-1.026782703436557</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.586298818335345</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.582793608044636</v>
+        <v>1.616858776457914</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.68610798886774</v>
+        <v>-10.62933270817894</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.107636779300465</v>
+        <v>-1.084926667024947</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.586298818335345</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.581318381145894</v>
+        <v>1.615383549559172</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.63651714444291</v>
+        <v>-10.57974186375411</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.072747031365659</v>
+        <v>-1.05003691909014</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.593483254599307</v>
+        <v>-2.536707973910511</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.626126297965667</v>
+        <v>1.660191466378945</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.62370975143813</v>
+        <v>-10.56693447074934</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.080675207810433</v>
+        <v>-1.057965095534914</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.642339029608209</v>
+        <v>-2.585563748919412</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.583761699313643</v>
+        <v>1.617826867726921</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.39786459871872</v>
+        <v>-10.34108931802993</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9807580736864598</v>
+        <v>-0.9580479614109412</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.543637073332248</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.61849677770215</v>
+        <v>1.652561946115428</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.27328594238113</v>
+        <v>-10.21651066169233</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9297874665953638</v>
+        <v>-0.9070773543198452</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.543637073332248</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.619635922258209</v>
+        <v>1.653701090671487</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.32618123042542</v>
+        <v>-10.26940594973662</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9483118076509713</v>
+        <v>-0.9256016953754527</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.538681727243802</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.625242904073384</v>
+        <v>1.659308072486662</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.25404805513754</v>
+        <v>-10.19727277444874</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9137248332971817</v>
+        <v>-0.891014721021663</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.538681727243802</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.630976608312021</v>
+        <v>1.665041776725299</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.18268166252789</v>
+        <v>-10.12590638183909</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8949155386471883</v>
+        <v>-0.8722054263716696</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.467315334634154</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.664059181483945</v>
+        <v>1.698124349897223</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08922262854266</v>
+        <v>-10.03244734785387</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8674154063660064</v>
+        <v>-0.8447052940904878</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.467315334634154</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.654175700171037</v>
+        <v>1.688240868584315</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.821980827674267</v>
+        <v>-9.76520554698547</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7623532465180207</v>
+        <v>-0.7396431342425021</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.467315334634154</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.652341139671663</v>
+        <v>1.686406308084941</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.724073788997776</v>
+        <v>-9.66729850830898</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7234907460208855</v>
+        <v>-0.7007806337453668</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.456104865462394</v>
+        <v>-2.399329584773597</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.692832274614536</v>
+        <v>1.726897443027814</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.700120248021818</v>
+        <v>-9.643344967333022</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7132408234850085</v>
+        <v>-0.6905307112094898</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.432151324486437</v>
+        <v>-2.37537604379764</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.707872905345605</v>
+        <v>1.741938073758883</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.436060309699021</v>
+        <v>-9.379285029010225</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6208771643176418</v>
+        <v>-0.5981670520421232</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.111316105474844</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.85304855217753</v>
+        <v>1.887113720590808</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.728980686194184</v>
+        <v>-8.672205405505387</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3408323485760079</v>
+        <v>-0.3181222363004892</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.111316105474844</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.850261518517229</v>
+        <v>1.884326686930507</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.688796387827994</v>
+        <v>-8.632021107139197</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3244150053416903</v>
+        <v>-0.3017048930661717</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.12790708779745</v>
+        <v>-2.071131807108653</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.874715721424785</v>
+        <v>1.908780889838063</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.52539651688863</v>
+        <v>-8.468621236199834</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.259688235745188</v>
+        <v>-0.2369781234696693</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.964507216858087</v>
+        <v>-1.907731936169291</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.972122465209159</v>
+        <v>2.006187633622437</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.291915294659031</v>
+        <v>-8.235140013970234</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.158371318015496</v>
+        <v>-0.1356612057399773</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731025994628489</v>
+        <v>-1.674250713939692</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.120135627384771</v>
+        <v>2.154200795798049</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.142248903651517</v>
+        <v>-8.08547362296272</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1013969719254493</v>
+        <v>-0.07868685964993061</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.638122503385953</v>
+        <v>-1.581347222697156</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172985511817333</v>
+        <v>2.207050680230611</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.009973430020629</v>
+        <v>-7.953198149331834</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05311929572606733</v>
+        <v>-0.0304091834505491</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.505847029755066</v>
+        <v>-1.449071749066269</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247718282742892</v>
+        <v>2.28178345115617</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.819373755347477</v>
+        <v>-7.762598474658681</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02593563483083017</v>
+        <v>0.04864574710634884</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.258472074393117</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.364893148234421</v>
+        <v>2.398958316647699</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.570373956663896</v>
+        <v>-7.5135986759751</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1384418955279214</v>
+        <v>0.1611520078034396</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.258472074393117</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.377799489458079</v>
+        <v>2.411864657871357</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.675963946437</v>
+        <v>-7.619188665748204</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03177002998053879</v>
+        <v>-0.00905991770502057</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.420837344855018</v>
+        <v>-1.364062064166221</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.186469565994998</v>
+        <v>2.220534734408276</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.694698848555597</v>
+        <v>-7.637923567866801</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.009280351049108404</v>
+        <v>0.03199046332462707</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.426433354515149</v>
+        <v>-1.369658073826352</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.231656302076006</v>
+        <v>2.265721470489284</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.546758807147998</v>
+        <v>-7.489983526459202</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05142255507601945</v>
+        <v>-0.02871244280050078</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.406112438606591</v>
+        <v>-1.349337157917795</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.123969928932973</v>
+        <v>2.158035097346251</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.493789284894009</v>
+        <v>-7.437014004205214</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03894873242790187</v>
+        <v>-0.01623862015238364</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.296367635663806</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.147037656031888</v>
+        <v>2.181102824445166</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.450240878123319</v>
+        <v>-7.393465597434523</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02848998181471885</v>
+        <v>-0.005779869539200622</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.296367635663806</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.140077043936795</v>
+        <v>2.174142212350073</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.208092484669461</v>
+        <v>-7.151317203980665</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0828317299479675</v>
+        <v>0.1055418422234857</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.296367635663806</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.154539398317938</v>
+        <v>2.188604566731216</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.099833347546939</v>
+        <v>-7.043058066858143</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1206675052561712</v>
+        <v>0.1433776175316894</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.296367635663806</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.149071518777133</v>
+        <v>2.183136687190411</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.976542212729808</v>
+        <v>-6.919766932041012</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1674820531936003</v>
+        <v>0.1901921654691185</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.229851781535472</v>
+        <v>-1.173076500846675</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.220544293677988</v>
+        <v>2.254609462091266</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.955393013826365</v>
+        <v>-6.898617733137569</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1836427109923027</v>
+        <v>0.2063528232678209</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.151927301943232</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.240934791257379</v>
+        <v>2.274999959670657</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.711627571842921</v>
+        <v>-6.654852291154125</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2769295961327312</v>
+        <v>0.2996397084082494</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.151927301943232</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.23671549960443</v>
+        <v>2.270780668017708</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.609864751565626</v>
+        <v>-6.55308947087683</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.319759038163665</v>
+        <v>0.3424691504391832</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.138708233550803</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246771254559903</v>
+        <v>2.280836422973181</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.360014357616551</v>
+        <v>-6.303239076927755</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4124412707269971</v>
+        <v>0.4351513830025153</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.138708233550803</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239513329543605</v>
+        <v>2.273578497956883</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.184122265149119</v>
+        <v>-6.127346984460322</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4863972312346188</v>
+        <v>0.5091073435101374</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.138708233550803</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.243112453064254</v>
+        <v>2.277177621477532</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.012675802126656</v>
+        <v>-5.955900521437859</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5683033224981577</v>
+        <v>0.5910134347736764</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.024037051217137</v>
+        <v>-0.9672617705283401</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.359307836932286</v>
+        <v>2.393373005345564</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.938386236388316</v>
+        <v>-5.88161095569952</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5970396264097904</v>
+        <v>0.619749738685309</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9497474854787973</v>
+        <v>-0.8929722047900008</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.402902053991586</v>
+        <v>2.436967222404864</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.874750494154382</v>
+        <v>-5.817975213465585</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6271887243576817</v>
+        <v>0.6498988366332004</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.8293364625560663</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.445778300386264</v>
+        <v>2.479843468799542</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.763323734828462</v>
+        <v>-5.706548454139665</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6529536868718453</v>
+        <v>0.675663799147364</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.8293364625560663</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.42697255917006</v>
+        <v>2.461037727583338</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.522893238023602</v>
+        <v>-5.466117957334805</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7508689622186666</v>
+        <v>0.7735790744941853</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.588905965751206</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.572973933877853</v>
+        <v>2.607039102291131</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.450650669852407</v>
+        <v>-5.39387538916361</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7836953033219647</v>
+        <v>0.8064054155974834</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.588905965751206</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.576903247712674</v>
+        <v>2.610968416125952</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.397652347571019</v>
+        <v>-5.340877066882222</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8055732161518598</v>
+        <v>0.8282833284273785</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5335697067492672</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.644848755444455</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.288847462091292</v>
+        <v>-5.232072181402495</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8460932415637443</v>
+        <v>0.868803353839263</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.5335697067492672</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.641846826664448</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.151784769604504</v>
+        <v>-5.08944071806316</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9024973555690736</v>
+        <v>0.9274349761856113</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.561899511676352</v>
+        <v>-0.5034589821309248</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.626427980718812</v>
+        <v>2.661492298446068</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.018917080541226</v>
+        <v>-4.956573028999882</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9715386139962079</v>
+        <v>0.9964762346127456</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.561899511676352</v>
+        <v>-0.5034589821309248</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.642322163520635</v>
+        <v>2.677386481247891</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.898743997176727</v>
+        <v>-4.836399945635383</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.020753691782309</v>
+        <v>1.045691312398847</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.441726428311853</v>
+        <v>-0.3832858987664258</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.715571857979636</v>
+        <v>2.750636175706892</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.75407185207699</v>
+        <v>-4.691727800535646</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.088710652383644</v>
+        <v>1.113648273000182</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2970542832121156</v>
+        <v>-0.2386137536666884</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.812463247600919</v>
+        <v>2.847527565328175</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.813946679434682</v>
+        <v>-4.751602627893338</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.050798212841993</v>
+        <v>1.075735833458531</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3569291105698078</v>
+        <v>-0.2984885810243805</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.762575842587729</v>
+        <v>2.797640160314985</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.727147181655674</v>
+        <v>-4.664803130114329</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.107918505276162</v>
+        <v>1.132856125892701</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3569291105698078</v>
+        <v>-0.2984885810243805</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.784976335910295</v>
+        <v>2.820040653637551</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.72961688811748</v>
+        <v>-4.667272836576135</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.107003024064852</v>
+        <v>1.13194064468139</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3593988170316139</v>
+        <v>-0.3009582874861867</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.783566913406624</v>
+        <v>2.81863123113388</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.79798707444149</v>
+        <v>-4.735643022900145</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.09066187200995</v>
+        <v>1.115599492626488</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.350123117995399</v>
+        <v>-0.2916825884499717</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.800139255303054</v>
+        <v>2.835203573030311</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.906525255357624</v>
+        <v>-4.844181203816279</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.037683308275388</v>
+        <v>1.062620928891926</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.350123117995399</v>
+        <v>-0.2916825884499717</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.790575963934946</v>
+        <v>2.825640281662202</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.93751841468633</v>
+        <v>-4.875174363144985</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8499956095842927</v>
+        <v>0.8749332302008306</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.350123117995399</v>
+        <v>-0.2916825884499717</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.615285528975333</v>
+        <v>2.650349846702589</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.762044154893861</v>
+        <v>-4.699700103352516</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9247525454930678</v>
+        <v>0.9496901661096058</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.350123117995399</v>
+        <v>-0.2916825884499717</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.61985276096712</v>
+        <v>2.654917078694377</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.87298040753511</v>
+        <v>-4.810636355993765</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8561200731977754</v>
+        <v>0.8810576938143133</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.350123117995399</v>
+        <v>-0.2916825884499717</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.595594789728327</v>
+        <v>2.630659107455584</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.881262481680168</v>
+        <v>-4.818918430138823</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8559386287596575</v>
+        <v>0.8808762493761955</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3584051921404574</v>
+        <v>-0.2999646625950301</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.593756930461198</v>
+        <v>2.628821248188454</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.821409862476445</v>
+        <v>-4.7590658109351</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8900520628732791</v>
+        <v>0.914989683489817</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3584051921404574</v>
+        <v>-0.2999646625950301</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.60392931689333</v>
+        <v>2.638993634620586</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.735166399450067</v>
+        <v>-4.672822347908722</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9194957186576906</v>
+        <v>0.9444333392742286</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3584051921404574</v>
+        <v>-0.2999646625950301</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.59887558746719</v>
+        <v>2.633939905194447</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.780473218849047</v>
+        <v>-4.718129167307702</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8931487663426241</v>
+        <v>0.9180863869591622</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3992153551496881</v>
+        <v>-0.3407748256042609</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.566165265106178</v>
+        <v>2.601229582833434</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.809506323551348</v>
+        <v>-4.747162272010003</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8820873974948054</v>
+        <v>0.9070250181113433</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3992153551496881</v>
+        <v>-0.3407748256042609</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.566717138139279</v>
+        <v>2.601781455866536</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.716695842100489</v>
+        <v>-4.654351790559144</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8484842819665148</v>
+        <v>0.8734219025830527</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3064048736988288</v>
+        <v>-0.2479643441534016</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.551676118901161</v>
+        <v>2.586740436628417</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.761085311429916</v>
+        <v>-4.698741259888571</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8326019701593446</v>
+        <v>0.8575395907758825</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3507943430282565</v>
+        <v>-0.2923538134828292</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.526915913228104</v>
+        <v>2.561980230955361</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.648414093193666</v>
+        <v>-4.586070041652321</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8727461659655678</v>
+        <v>0.8976837865821057</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2381231247920063</v>
+        <v>-0.179682595246579</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.589594352681578</v>
+        <v>2.624658670408834</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.536037092010993</v>
+        <v>-4.473693040469648</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9231882622693042</v>
+        <v>0.9481258828858421</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2381231247920063</v>
+        <v>-0.179682595246579</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.595085648512245</v>
+        <v>2.630149966239501</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.563817489912346</v>
+        <v>-4.501473438371001</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.923573304877302</v>
+        <v>0.94851092549384</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2659035226933593</v>
+        <v>-0.2074629931479321</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.589914611539972</v>
+        <v>2.624978929267229</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.646818770937625</v>
+        <v>-4.58447471939628</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7287285124678438</v>
+        <v>0.7536661330843817</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2844744072205331</v>
+        <v>-0.2260338776751059</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.417127800824321</v>
+        <v>2.452192118551578</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.755432849380956</v>
+        <v>-4.693088797839611</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.805432541809717</v>
+        <v>0.8303701624262549</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2844744072205331</v>
+        <v>-0.2260338776751059</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.537277461543527</v>
+        <v>2.572341779270783</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.842031432362059</v>
+        <v>-4.779687380820714</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7853061347195989</v>
+        <v>0.8102437553361368</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2844744072205331</v>
+        <v>-0.2260338776751059</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.55179048764585</v>
+        <v>2.586854805373106</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.803647769803908</v>
+        <v>-4.741303718262563</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7980790410852279</v>
+        <v>0.8230166617017658</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2460907446623819</v>
+        <v>-0.1876502151169547</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.572240126523109</v>
+        <v>2.607304444250365</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.626531439768741</v>
+        <v>-4.564187388227396</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8656546019445963</v>
+        <v>0.8905922225611342</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2460907446623819</v>
+        <v>-0.1876502151169547</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.568969155368411</v>
+        <v>2.604033473095667</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.671623684602287</v>
+        <v>-4.609279633060942</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.848301095773091</v>
+        <v>0.8732387163896291</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3079867878317717</v>
+        <v>-0.2495462582863445</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.532514921228691</v>
+        <v>2.567579238955947</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.492248263363519</v>
+        <v>-4.429904211822175</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9138382395750124</v>
+        <v>0.9387758601915506</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.151210029661053</v>
+        <v>-0.09276950011562579</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.620367951437536</v>
+        <v>2.655432269164792</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.537262476884125</v>
+        <v>-4.47491842534278</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.87664000949836</v>
+        <v>0.9015776301148979</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1815589249756576</v>
+        <v>-0.1231183954302304</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.582966069580363</v>
+        <v>2.618030387307619</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.526360401043842</v>
+        <v>-4.741922935615215</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.886692402173419</v>
+        <v>0.8004673883448696</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1528454256908336</v>
+        <v>-0.317481433473179</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.605885731490203</v>
+        <v>2.507104126820796</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.627558182481015</v>
+        <v>-4.843120717052388</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8454172114950513</v>
+        <v>0.7591921976665019</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2212542392361528</v>
+        <v>-0.3858902470184982</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.564044365259513</v>
+        <v>2.465262760590106</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.595082596310243</v>
+        <v>-4.810645130881616</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8560074075176769</v>
+        <v>0.7697823936891277</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2212542392361528</v>
+        <v>-0.3858902470184982</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.56164432681383</v>
+        <v>2.462862722144423</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.576044468602945</v>
+        <v>-4.791607003174319</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8601473778088407</v>
+        <v>0.7739223639802915</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2794378505673473</v>
+        <v>-0.4440738583496927</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.523258879223358</v>
+        <v>2.424477274553951</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.607171099753564</v>
+        <v>-4.822733634324937</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.025278594287274</v>
+        <v>0.9390535804587246</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2794378505673473</v>
+        <v>-0.4440738583496927</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.700840748162038</v>
+        <v>2.602059143492631</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.621037861087482</v>
+        <v>-4.836600395658855</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.02056521873984</v>
+        <v>0.934340204911291</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3172957673011703</v>
+        <v>-0.4819317750835156</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.678959327107878</v>
+        <v>2.580177722438471</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.64129515961644</v>
+        <v>-4.856857694187813</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.018470829725183</v>
+        <v>0.9322458158966338</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3172957673011703</v>
+        <v>-0.4819317750835156</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.684967857504804</v>
+        <v>2.586186252835397</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.493552189381437</v>
+        <v>-4.70911472395281</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.156720665611206</v>
+        <v>1.070495651782657</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1494884100662871</v>
+        <v>-0.3141244178486325</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.864804919637756</v>
+        <v>2.766023314968349</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.595566871912658</v>
+        <v>-4.811129406484032</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.118708414130198</v>
+        <v>1.032483400301649</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1494884100662871</v>
+        <v>-0.3141244178486325</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.867598541169237</v>
+        <v>2.76881693649983</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.589414165859874</v>
+        <v>-4.804976700431247</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.121831844942971</v>
+        <v>1.035606831114421</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1433357040135028</v>
+        <v>-0.3079717117958482</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.871952513192566</v>
+        <v>2.773170908523159</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.606223464010376</v>
+        <v>-4.821785998581749</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.11418860242288</v>
+        <v>1.027963588594331</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1601450021640045</v>
+        <v>-0.3247810099463498</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.860947411042375</v>
+        <v>2.762165806372968</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.543925465234254</v>
+        <v>-4.759487999805627</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.20544335573015</v>
+        <v>1.119218341901601</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1601450021640045</v>
+        <v>-0.3247810099463498</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.927282964839196</v>
+        <v>2.828501360169789</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.342135267569096</v>
+        <v>-4.557697802140469</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9947403071856111</v>
+        <v>0.9085152933570617</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.03787319000514994</v>
+        <v>-0.1267628177771954</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.754674752530087</v>
+        <v>2.65589314786068</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.282244585926502</v>
+        <v>-4.497807120497876</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.088986812164824</v>
+        <v>1.002761798336274</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.09776387164774342</v>
+        <v>-0.06687213613460197</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.860899393837818</v>
+        <v>2.762117789168411</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.379985130551477</v>
+        <v>-4.59554766512285</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.064518330430877</v>
+        <v>0.9782933166023282</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.08187459351476323</v>
+        <v>-0.08276141426758216</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.865993563074074</v>
+        <v>2.767211958404666</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.556322890674406</v>
+        <v>-4.771885425245779</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9925192072063775</v>
+        <v>0.9062941933778281</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.09446316660816617</v>
+        <v>-0.2590991743905116</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.758726887824988</v>
+        <v>2.65994528315558</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.484776567897529</v>
+        <v>-4.700339102468902</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.019629354357057</v>
+        <v>0.9334043405285075</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.09446316660816617</v>
+        <v>-0.2590991743905116</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.757218505864916</v>
+        <v>2.658436901195509</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.44040343625896</v>
+        <v>-4.655965970830334</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.03724147444792</v>
+        <v>0.9510164606193712</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.05009003496959757</v>
+        <v>-0.214726042751943</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.783705252283494</v>
+        <v>2.684923647614086</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.432449465964188</v>
+        <v>-4.648012000535561</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.040423062565829</v>
+        <v>0.9541980487372801</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.05009003496959757</v>
+        <v>-0.214726042751943</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.783705252283494</v>
+        <v>2.684923647614086</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.384793735403132</v>
+        <v>-4.600356269974506</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.065867111818056</v>
+        <v>0.9796420979895071</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.002434304408541921</v>
+        <v>-0.1670703121908873</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.818680447647932</v>
+        <v>2.719898842978524</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.257109425608836</v>
+        <v>-4.472671960180209</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.1218332091105</v>
+        <v>1.03560819528195</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1252500053857545</v>
+        <v>-0.03938600239659085</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.900183406899234</v>
+        <v>2.801401802229827</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.317776016011225</v>
+        <v>-4.533338550582599</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.084321245425417</v>
+        <v>0.9980962315968669</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.04355168866722087</v>
+        <v>-0.1210843191151245</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.837919089343986</v>
+        <v>2.739137484674579</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.272937614402826</v>
+        <v>-4.4885001489742</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.106354308679404</v>
+        <v>1.020129294850855</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.04809512161209034</v>
+        <v>-0.116540886170255</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.844742851721537</v>
+        <v>2.745961247052129</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.373696250159824</v>
+        <v>-4.589258784731198</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.070211794007683</v>
+        <v>0.9839867801791335</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.04073044711491508</v>
+        <v>-0.2053664548972605</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.795608450116411</v>
+        <v>2.696826845447004</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.329493413073924</v>
+        <v>-4.545055947645298</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.093772531369881</v>
+        <v>1.007547517541331</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.003472389970985368</v>
+        <v>-0.16116361781136</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.828009754895789</v>
+        <v>2.729228150226382</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.366472440737367</v>
+        <v>-4.582034975308741</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.077390920773751</v>
+        <v>0.9911659069452012</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.0404462917623159</v>
+        <v>-0.1241897160200295</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.848604096439835</v>
+        <v>2.749822491770427</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.386530519602207</v>
+        <v>-4.602093054173581</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.120615454410854</v>
+        <v>1.034390440582305</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.0404462917623159</v>
+        <v>-0.1241897160200295</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.899851861622874</v>
+        <v>2.801070256953467</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.346599846424317</v>
+        <v>-4.562162380995691</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.135028428276264</v>
+        <v>1.048803414447714</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.08037696494020624</v>
+        <v>-0.08425904284213914</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.922250970123862</v>
+        <v>2.823469365454454</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.295567753701789</v>
+        <v>-4.511130288273163</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.150389493603545</v>
+        <v>1.064164479774995</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1314090576627342</v>
+        <v>-0.03322695011961119</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.947818453995648</v>
+        <v>2.849036849326241</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.230343572574584</v>
+        <v>-4.445906107145958</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.193666570147132</v>
+        <v>1.107441556318582</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1966332387899398</v>
+        <v>0.03199723100759444</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.004140366764677</v>
+        <v>2.90535876209527</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.19291655250345</v>
+        <v>-4.408479087074824</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.204598350474866</v>
+        <v>1.118373336646316</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.2018847768191215</v>
+        <v>0.0372487690367761</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.003252261881466</v>
+        <v>2.904470657212059</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.845198842749922</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.213028208538158</v>
+        <v>-4.428590743109532</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.197810480392223</v>
+        <v>1.111585466563673</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.2129121218165407</v>
+        <v>0.04827611403419529</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.011125461211158</v>
+        <v>2.912343856541751</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.310708787810803</v>
+        <v>-4.526271322382177</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.319296019704375</v>
+        <v>1.233071005875826</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.1022089264763519</v>
+        <v>-0.0624270813059935</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.105261315028256</v>
+        <v>3.006479710358848</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.286917219204661</v>
+        <v>-4.502479753776035</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.44892555636465</v>
+        <v>1.3627005425361</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.1260004950824942</v>
+        <v>-0.03863551269985122</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.239649165409758</v>
+        <v>3.140867560740351</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.323671637766383</v>
+        <v>-4.539234172337757</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.42593176495382</v>
+        <v>1.33970675112527</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.1260004950824942</v>
+        <v>-0.03863551269985122</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.231357141423617</v>
+        <v>3.13257553675421</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.319337334709335</v>
+        <v>-4.534899869280709</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.425858681760418</v>
+        <v>1.339633667931869</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2776505984016981</v>
+        <v>0.1130145906193527</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.320540398998919</v>
+        <v>3.221758794329511</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.310444873316052</v>
+        <v>-4.526007407887426</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.446970072044523</v>
+        <v>1.360745058215973</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2776505984016981</v>
+        <v>0.1130145906193527</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.33809480472571</v>
+        <v>3.239313200056303</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.478920990285929</v>
+        <v>-4.694483524857303</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.371434672661156</v>
+        <v>1.285209658832606</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.2497027626851173</v>
+        <v>0.08506675490277193</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.313181150700346</v>
+        <v>3.214399546030938</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.781121461424346</v>
+        <v>-3.99668399599572</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.720967145662633</v>
+        <v>1.634742131834083</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1793547033147066</v>
+        <v>0.01471869553236121</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.341384976534943</v>
+        <v>3.242603371865536</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.758400357741194</v>
+        <v>-3.973962892312568</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.720719609632799</v>
+        <v>1.634494595804249</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1793547033147066</v>
+        <v>0.01471869553236121</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.332048999031847</v>
+        <v>3.23326739436244</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.885129387023484</v>
+        <v>3.783234730534935</v>
       </c>
       <c r="C1999" t="n">
         <v>3.383342302894192</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.898692957278386</v>
+        <v>-4.11425549184976</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.823508695669091</v>
+        <v>1.737283681840541</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.03906210377751396</v>
+        <v>-0.1255739040048314</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.406779565160701</v>
+        <v>3.307997960491293</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.577673724346472</v>
+        <v>3.813938510120282</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.380912392875386</v>
+        <v>3.243543751439944</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.81994907345022</v>
+        <v>-4.167041455549384</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.852576339181551</v>
+        <v>1.576370744906443</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.1550002467526382</v>
+        <v>-0.1442863200478602</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.473912540926969</v>
+        <v>3.156971959411228</v>
       </c>
     </row>
   </sheetData>
